--- a/projects/paper-02/04-extract/数据_7_数据提取表_v1.xlsx
+++ b/projects/paper-02/04-extract/数据_7_数据提取表_v1.xlsx
@@ -9424,15 +9424,15 @@
   </sheetData>
   <autoFilter ref="A2:AK2"/>
   <mergeCells count="7">
-    <mergeCell ref="AF1:AI1"/>
     <mergeCell ref="AC1:AE1"/>
     <mergeCell ref="AJ1:AK1"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="J1:N1"/>
+    <mergeCell ref="AF1:AI1"/>
+    <mergeCell ref="V1:AB1"/>
     <mergeCell ref="O1:U1"/>
-    <mergeCell ref="V1:AB1"/>
   </mergeCells>
-  <dataValidations count="13">
+  <dataValidations count="14">
     <dataValidation sqref="E4:E203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"横断,纵向,RCT子分析"</formula1>
     </dataValidation>
@@ -9472,6 +9472,9 @@
     <dataValidation sqref="AK4:AK203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"oo,cc"</formula1>
     </dataValidation>
+    <dataValidation sqref="Y4:Y203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"positive,negative,null,mixed"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/projects/paper-02/04-extract/数据_7_数据提取表_v1.xlsx
+++ b/projects/paper-02/04-extract/数据_7_数据提取表_v1.xlsx
@@ -1022,214 +1022,864 @@
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="16" t="n"/>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16" t="n"/>
-      <c r="H4" s="16" t="n"/>
-      <c r="I4" s="16" t="n"/>
-      <c r="J4" s="16" t="n"/>
-      <c r="K4" s="16" t="n"/>
-      <c r="L4" s="16" t="n"/>
-      <c r="M4" s="16" t="n"/>
-      <c r="N4" s="16" t="n"/>
-      <c r="O4" s="16" t="n"/>
-      <c r="P4" s="16" t="n"/>
-      <c r="Q4" s="16" t="n"/>
-      <c r="R4" s="16" t="n"/>
-      <c r="S4" s="16" t="n"/>
-      <c r="T4" s="16" t="n"/>
-      <c r="U4" s="16" t="n"/>
-      <c r="V4" s="16" t="n"/>
-      <c r="W4" s="16" t="n"/>
-      <c r="X4" s="16" t="n"/>
-      <c r="Y4" s="16" t="n"/>
-      <c r="Z4" s="16" t="n"/>
-      <c r="AA4" s="16" t="n"/>
-      <c r="AB4" s="16" t="n"/>
-      <c r="AC4" s="16" t="n"/>
-      <c r="AD4" s="16" t="n"/>
-      <c r="AE4" s="16" t="n"/>
-      <c r="AF4" s="16" t="n"/>
-      <c r="AG4" s="16" t="n"/>
-      <c r="AH4" s="16" t="n"/>
+      <c r="A4" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Wienke</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>横断</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>255</v>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>6–14 months (M=8.3)</t>
+        </is>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="16" t="inlineStr">
+        <is>
+          <t>infant(1-12m)</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="inlineStr">
+        <is>
+          <t>父母是否有大学入学资格（二分：低教育=双亲均无university entrance degree；高教育=至少一方有）</t>
+        </is>
+      </c>
+      <c r="K4" s="16" t="inlineStr">
+        <is>
+          <t>单独报告</t>
+        </is>
+      </c>
+      <c r="L4" s="16" t="inlineStr">
+        <is>
+          <t>二分</t>
+        </is>
+      </c>
+      <c r="M4" s="16" t="inlineStr">
+        <is>
+          <t>group-comparison</t>
+        </is>
+      </c>
+      <c r="N4" s="16" t="inlineStr">
+        <is>
+          <t>移民背景（migration background）</t>
+        </is>
+      </c>
+      <c r="O4" s="16" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+      <c r="P4" s="16" t="inlineStr">
+        <is>
+          <t>N2–P3a complex amplitude</t>
+        </is>
+      </c>
+      <c r="Q4" s="16" t="inlineStr">
+        <is>
+          <t>任务态-oddball</t>
+        </is>
+      </c>
+      <c r="R4" s="16" t="inlineStr">
+        <is>
+          <t>混合线性模型（ANOVA with repeated measures）</t>
+        </is>
+      </c>
+      <c r="S4" s="16" t="inlineStr">
+        <is>
+          <t>F7/F8, FC5/FC6（前额中央区）</t>
+        </is>
+      </c>
+      <c r="T4" s="16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U4" s="16" t="inlineStr">
+        <is>
+          <t>BRISE（Bremen Initiative to Foster Early Childhood Development）</t>
+        </is>
+      </c>
+      <c r="V4" s="16" t="inlineStr">
+        <is>
+          <t>显著负相关</t>
+        </is>
+      </c>
+      <c r="W4" s="16" t="inlineStr">
+        <is>
+          <t>低父母教育（双亲均无高中毕业文凭）组婴儿N2–P3a振幅更偏正（deviant处理偏差加大），提示早期神经注意加工延迟（EDU1/MIG1 vs EDU0/MIG0, p=0.037）</t>
+        </is>
+      </c>
+      <c r="X4" s="16" t="inlineStr">
+        <is>
+          <t>Group effect F(3,250)=2.7, p=0.049, η²=0.03; group×stimulus F(3,250)=5.0, p=0.002, η²=0.06; post-hoc EDU1/MIG1 vs EDU0/MIG0 deviant p=0.001</t>
+        </is>
+      </c>
+      <c r="Y4" s="16" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Z4" s="16" t="inlineStr">
+        <is>
+          <t>重复测量方差分析（mixed ANOVA）</t>
+        </is>
+      </c>
+      <c r="AA4" s="16" t="inlineStr">
+        <is>
+          <t>年龄（月龄）</t>
+        </is>
+      </c>
+      <c r="AB4" s="16" t="inlineStr">
+        <is>
+          <t>未检验中介/调节</t>
+        </is>
+      </c>
+      <c r="AC4" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AD4" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AE4" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AF4" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG4" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="16" t="n">
+        <v>2</v>
+      </c>
       <c r="AI4" s="17">
         <f>IFERROR(AF4+AG4+AH4,"")</f>
         <v/>
       </c>
-      <c r="AJ4" s="16" t="n"/>
-      <c r="AK4" s="16" t="n"/>
+      <c r="AJ4" s="16" t="inlineStr">
+        <is>
+          <t>低教育组定义为双亲均无高中毕业文凭（≤10年教育）；迁移背景作为第二分组变量，两变量交叉形成4组；未单独报告父母教育主效应（仅教育+移民联合组差异显著）</t>
+        </is>
+      </c>
+      <c r="AK4" s="16" t="inlineStr">
+        <is>
+          <t>oo</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="16" t="n"/>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16" t="n"/>
-      <c r="H5" s="16" t="n"/>
-      <c r="I5" s="16" t="n"/>
-      <c r="J5" s="16" t="n"/>
-      <c r="K5" s="16" t="n"/>
-      <c r="L5" s="16" t="n"/>
-      <c r="M5" s="16" t="n"/>
-      <c r="N5" s="16" t="n"/>
-      <c r="O5" s="16" t="n"/>
-      <c r="P5" s="16" t="n"/>
-      <c r="Q5" s="16" t="n"/>
-      <c r="R5" s="16" t="n"/>
-      <c r="S5" s="16" t="n"/>
-      <c r="T5" s="16" t="n"/>
-      <c r="U5" s="16" t="n"/>
-      <c r="V5" s="16" t="n"/>
-      <c r="W5" s="16" t="n"/>
-      <c r="X5" s="16" t="n"/>
-      <c r="Y5" s="16" t="n"/>
-      <c r="Z5" s="16" t="n"/>
-      <c r="AA5" s="16" t="n"/>
-      <c r="AB5" s="16" t="n"/>
-      <c r="AC5" s="16" t="n"/>
-      <c r="AD5" s="16" t="n"/>
-      <c r="AE5" s="16" t="n"/>
-      <c r="AF5" s="16" t="n"/>
-      <c r="AG5" s="16" t="n"/>
-      <c r="AH5" s="16" t="n"/>
+      <c r="A5" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Wijeakumar</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>横断</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>5–8 years</t>
+        </is>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>early-school(6-8y)</t>
+        </is>
+      </c>
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t>母亲受教育年数（连续变量）</t>
+        </is>
+      </c>
+      <c r="K5" s="16" t="inlineStr">
+        <is>
+          <t>单独报告</t>
+        </is>
+      </c>
+      <c r="L5" s="16" t="inlineStr">
+        <is>
+          <t>连续变量</t>
+        </is>
+      </c>
+      <c r="M5" s="16" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="N5" s="16" t="inlineStr">
+        <is>
+          <t>家庭收入</t>
+        </is>
+      </c>
+      <c r="O5" s="16" t="inlineStr">
+        <is>
+          <t>fNIRS</t>
+        </is>
+      </c>
+      <c r="P5" s="16" t="inlineStr">
+        <is>
+          <t>HbO activation (oxyhaemoglobin)</t>
+        </is>
+      </c>
+      <c r="Q5" s="16" t="inlineStr">
+        <is>
+          <t>任务态-other</t>
+        </is>
+      </c>
+      <c r="R5" s="16" t="inlineStr">
+        <is>
+          <t>全脑fNIRS激活分析（GLM）</t>
+        </is>
+      </c>
+      <c r="S5" s="16" t="inlineStr">
+        <is>
+          <t>lDLPFC1 (L dorsolateral PFC), lIFG1 (L inferior frontal gyrus)</t>
+        </is>
+      </c>
+      <c r="T5" s="16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U5" s="16" t="inlineStr">
+        <is>
+          <t>未命名队列（rural Uttar Pradesh, India）</t>
+        </is>
+      </c>
+      <c r="V5" s="16" t="inlineStr">
+        <is>
+          <t>显著正相关</t>
+        </is>
+      </c>
+      <c r="W5" s="16" t="inlineStr">
+        <is>
+          <t>母亲教育年数越高，视觉工作记忆任务高负荷下左侧DLPFC和IFG的HbO激活越强（lDLPFC1: F(1,33)=5.594, p&lt;0.05, R²=0.149；lIFG1: F(1,32)=6.387, p&lt;0.05, R²=0.166）</t>
+        </is>
+      </c>
+      <c r="X5" s="16" t="inlineStr">
+        <is>
+          <t>lDLPFC1: F(1,33)=5.594, p&lt;0.05, R²=0.149; lIFG1: F(1,32)=6.387, p&lt;0.05, R²=0.166</t>
+        </is>
+      </c>
+      <c r="Y5" s="16" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Z5" s="16" t="inlineStr">
+        <is>
+          <t>简单线性回归（逐步回归比较收入vs教育）</t>
+        </is>
+      </c>
+      <c r="AA5" s="16" t="inlineStr">
+        <is>
+          <t>儿童年龄、性别</t>
+        </is>
+      </c>
+      <c r="AB5" s="16" t="inlineStr">
+        <is>
+          <t>逐步回归确认母亲教育独立于家庭收入解释HbO激活方差</t>
+        </is>
+      </c>
+      <c r="AC5" s="16" t="inlineStr">
+        <is>
+          <t>认知刺激</t>
+        </is>
+      </c>
+      <c r="AD5" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AE5" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AF5" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG5" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="16" t="n">
+        <v>2</v>
+      </c>
       <c r="AI5" s="17">
         <f>IFERROR(AF5+AG5+AH5,"")</f>
         <v/>
       </c>
-      <c r="AJ5" s="16" t="n"/>
-      <c r="AK5" s="16" t="n"/>
+      <c r="AJ5" s="16" t="inlineStr">
+        <is>
+          <t>样本为印度农村低SES儿童（Rural UP）；收入也显著预测IFG激活；逐步回归结果未明确报告哪个变量解释更多方差</t>
+        </is>
+      </c>
+      <c r="AK5" s="16" t="inlineStr">
+        <is>
+          <t>oo</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="16" t="n"/>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
-      <c r="G6" s="16" t="n"/>
-      <c r="H6" s="16" t="n"/>
-      <c r="I6" s="16" t="n"/>
-      <c r="J6" s="16" t="n"/>
-      <c r="K6" s="16" t="n"/>
-      <c r="L6" s="16" t="n"/>
-      <c r="M6" s="16" t="n"/>
-      <c r="N6" s="16" t="n"/>
-      <c r="O6" s="16" t="n"/>
-      <c r="P6" s="16" t="n"/>
-      <c r="Q6" s="16" t="n"/>
-      <c r="R6" s="16" t="n"/>
-      <c r="S6" s="16" t="n"/>
-      <c r="T6" s="16" t="n"/>
-      <c r="U6" s="16" t="n"/>
-      <c r="V6" s="16" t="n"/>
-      <c r="W6" s="16" t="n"/>
-      <c r="X6" s="16" t="n"/>
-      <c r="Y6" s="16" t="n"/>
-      <c r="Z6" s="16" t="n"/>
-      <c r="AA6" s="16" t="n"/>
-      <c r="AB6" s="16" t="n"/>
-      <c r="AC6" s="16" t="n"/>
-      <c r="AD6" s="16" t="n"/>
-      <c r="AE6" s="16" t="n"/>
-      <c r="AF6" s="16" t="n"/>
-      <c r="AG6" s="16" t="n"/>
-      <c r="AH6" s="16" t="n"/>
+      <c r="A6" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Stiver</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>2015</v>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>纵向</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>纵向: 早产后2周、足月矫正龄、2岁矫正龄</t>
+        </is>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>toddler(1-3y)</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>母亲是否完成大专及以上教育（postsecondary training or above，二分）</t>
+        </is>
+      </c>
+      <c r="K6" s="16" t="inlineStr">
+        <is>
+          <t>单独报告</t>
+        </is>
+      </c>
+      <c r="L6" s="16" t="inlineStr">
+        <is>
+          <t>二分</t>
+        </is>
+      </c>
+      <c r="M6" s="16" t="inlineStr">
+        <is>
+          <t>group-comparison</t>
+        </is>
+      </c>
+      <c r="N6" s="16" t="inlineStr">
+        <is>
+          <t>父亲教育（也报告但效应弱）</t>
+        </is>
+      </c>
+      <c r="O6" s="16" t="inlineStr">
+        <is>
+          <t>sMRI</t>
+        </is>
+      </c>
+      <c r="P6" s="16" t="inlineStr">
+        <is>
+          <t>小脑体积（cerebellar volume，cm³）</t>
+        </is>
+      </c>
+      <c r="Q6" s="16" t="inlineStr">
+        <is>
+          <t>结构</t>
+        </is>
+      </c>
+      <c r="R6" s="16" t="inlineStr">
+        <is>
+          <t>线性回归（纵向多时间点）</t>
+        </is>
+      </c>
+      <c r="S6" s="16" t="inlineStr">
+        <is>
+          <t>小脑（cerebellum）</t>
+        </is>
+      </c>
+      <c r="T6" s="16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U6" s="16" t="inlineStr">
+        <is>
+          <t>未命名队列（加拿大早产儿队列）</t>
+        </is>
+      </c>
+      <c r="V6" s="16" t="inlineStr">
+        <is>
+          <t>显著正相关</t>
+        </is>
+      </c>
+      <c r="W6" s="16" t="inlineStr">
+        <is>
+          <t>母亲完成大专及以上教育与早产儿2岁矫正龄时更大的小脑体积独立相关（P=0.006），足月等效龄时无显著差异（P=0.16）</t>
+        </is>
+      </c>
+      <c r="X6" s="16" t="inlineStr">
+        <is>
+          <t>P=0.006（2岁小脑体积）；P=0.16（足月等效龄小脑体积）</t>
+        </is>
+      </c>
+      <c r="Y6" s="16" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Z6" s="16" t="inlineStr">
+        <is>
+          <t>线性回归（控制胎龄、脑损伤等围产因素）</t>
+        </is>
+      </c>
+      <c r="AA6" s="16" t="inlineStr">
+        <is>
+          <t>胎龄、脑室出血（IVH）、白质损伤、小脑出血、产后类固醇暴露</t>
+        </is>
+      </c>
+      <c r="AB6" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AC6" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AD6" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AE6" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AF6" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG6" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH6" s="16" t="n">
+        <v>3</v>
+      </c>
       <c r="AI6" s="17">
         <f>IFERROR(AF6+AG6+AH6,"")</f>
         <v/>
       </c>
-      <c r="AJ6" s="16" t="n"/>
-      <c r="AK6" s="16" t="n"/>
+      <c r="AJ6" s="16" t="inlineStr">
+        <is>
+          <t>纯早产儿样本（&lt;34周）；样本量小（N=26）；父亲教育控制后母亲教育效应保持显著（P=0.01）</t>
+        </is>
+      </c>
+      <c r="AK6" s="16" t="inlineStr">
+        <is>
+          <t>oo</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="16" t="n"/>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
-      <c r="G7" s="16" t="n"/>
-      <c r="H7" s="16" t="n"/>
-      <c r="I7" s="16" t="n"/>
-      <c r="J7" s="16" t="n"/>
-      <c r="K7" s="16" t="n"/>
-      <c r="L7" s="16" t="n"/>
-      <c r="M7" s="16" t="n"/>
-      <c r="N7" s="16" t="n"/>
-      <c r="O7" s="16" t="n"/>
-      <c r="P7" s="16" t="n"/>
-      <c r="Q7" s="16" t="n"/>
-      <c r="R7" s="16" t="n"/>
-      <c r="S7" s="16" t="n"/>
-      <c r="T7" s="16" t="n"/>
-      <c r="U7" s="16" t="n"/>
-      <c r="V7" s="16" t="n"/>
-      <c r="W7" s="16" t="n"/>
-      <c r="X7" s="16" t="n"/>
-      <c r="Y7" s="16" t="n"/>
-      <c r="Z7" s="16" t="n"/>
-      <c r="AA7" s="16" t="n"/>
-      <c r="AB7" s="16" t="n"/>
-      <c r="AC7" s="16" t="n"/>
-      <c r="AD7" s="16" t="n"/>
-      <c r="AE7" s="16" t="n"/>
-      <c r="AF7" s="16" t="n"/>
-      <c r="AG7" s="16" t="n"/>
-      <c r="AH7" s="16" t="n"/>
+      <c r="A7" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Brito</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>横断</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>179</v>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>6–12 months (EEG); 15–21 months (language)</t>
+        </is>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>infant(1-12m)</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>母亲受教育年数（连续变量）</t>
+        </is>
+      </c>
+      <c r="K7" s="16" t="inlineStr">
+        <is>
+          <t>单独报告</t>
+        </is>
+      </c>
+      <c r="L7" s="16" t="inlineStr">
+        <is>
+          <t>连续变量</t>
+        </is>
+      </c>
+      <c r="M7" s="16" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="N7" s="16" t="inlineStr">
+        <is>
+          <t>家庭收入（income-to-needs ratio）</t>
+        </is>
+      </c>
+      <c r="O7" s="16" t="inlineStr">
+        <is>
+          <t>rsEEG</t>
+        </is>
+      </c>
+      <c r="P7" s="16" t="inlineStr">
+        <is>
+          <t>颞区beta频段功率（temporal beta EEG power）</t>
+        </is>
+      </c>
+      <c r="Q7" s="16" t="inlineStr">
+        <is>
+          <t>静息态</t>
+        </is>
+      </c>
+      <c r="R7" s="16" t="inlineStr">
+        <is>
+          <t>多元线性回归</t>
+        </is>
+      </c>
+      <c r="S7" s="16" t="inlineStr">
+        <is>
+          <t>颞区（temporal region）</t>
+        </is>
+      </c>
+      <c r="T7" s="16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U7" s="16" t="inlineStr">
+        <is>
+          <t>未命名队列（New York City双语家庭队列）</t>
+        </is>
+      </c>
+      <c r="V7" s="16" t="inlineStr">
+        <is>
+          <t>显著正相关</t>
+        </is>
+      </c>
+      <c r="W7" s="16" t="inlineStr">
+        <is>
+          <t>母亲教育年数越高，婴儿颞区beta频段EEG功率越大（β=0.05, p=0.025, adjusted R²=0.06），但FDR校正后不显著</t>
+        </is>
+      </c>
+      <c r="X7" s="16" t="inlineStr">
+        <is>
+          <t>β=0.05, p=0.025, adjusted R²=0.06（FDR未通过）</t>
+        </is>
+      </c>
+      <c r="Y7" s="16" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Z7" s="16" t="inlineStr">
+        <is>
+          <t>多元线性回归（控制年龄、性别、家庭ITN）</t>
+        </is>
+      </c>
+      <c r="AA7" s="16" t="inlineStr">
+        <is>
+          <t>儿童年龄、性别、家庭ITN</t>
+        </is>
+      </c>
+      <c r="AB7" s="16" t="inlineStr">
+        <is>
+          <t>未检验中介；语言环境（LENA指标）与EEG功率相关，但未正式中介分析</t>
+        </is>
+      </c>
+      <c r="AC7" s="16" t="inlineStr">
+        <is>
+          <t>语言输入</t>
+        </is>
+      </c>
+      <c r="AD7" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AE7" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AF7" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG7" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH7" s="16" t="n">
+        <v>2</v>
+      </c>
       <c r="AI7" s="17">
         <f>IFERROR(AF7+AG7+AH7,"")</f>
         <v/>
       </c>
-      <c r="AJ7" s="16" t="n"/>
-      <c r="AK7" s="16" t="n"/>
+      <c r="AJ7" s="16" t="inlineStr">
+        <is>
+          <t>FDR校正后边缘不显著；双语/单语家庭混合样本；家庭语言环境（AWC/CTC）与EEG功率关联更强</t>
+        </is>
+      </c>
+      <c r="AK7" s="16" t="inlineStr">
+        <is>
+          <t>oo</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="16" t="n"/>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n"/>
-      <c r="G8" s="16" t="n"/>
-      <c r="H8" s="16" t="n"/>
-      <c r="I8" s="16" t="n"/>
-      <c r="J8" s="16" t="n"/>
-      <c r="K8" s="16" t="n"/>
-      <c r="L8" s="16" t="n"/>
-      <c r="M8" s="16" t="n"/>
-      <c r="N8" s="16" t="n"/>
-      <c r="O8" s="16" t="n"/>
-      <c r="P8" s="16" t="n"/>
-      <c r="Q8" s="16" t="n"/>
-      <c r="R8" s="16" t="n"/>
-      <c r="S8" s="16" t="n"/>
-      <c r="T8" s="16" t="n"/>
-      <c r="U8" s="16" t="n"/>
-      <c r="V8" s="16" t="n"/>
-      <c r="W8" s="16" t="n"/>
-      <c r="X8" s="16" t="n"/>
-      <c r="Y8" s="16" t="n"/>
-      <c r="Z8" s="16" t="n"/>
-      <c r="AA8" s="16" t="n"/>
-      <c r="AB8" s="16" t="n"/>
-      <c r="AC8" s="16" t="n"/>
-      <c r="AD8" s="16" t="n"/>
-      <c r="AE8" s="16" t="n"/>
-      <c r="AF8" s="16" t="n"/>
-      <c r="AG8" s="16" t="n"/>
-      <c r="AH8" s="16" t="n"/>
+      <c r="A8" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>McKinnon</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>横断</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>261</v>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>足月矫正龄（neonatal，足月及早产儿）</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>neonatal(0-1m)</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>母亲受教育年数或学历等级（连续变量）；父亲教育也分析</t>
+        </is>
+      </c>
+      <c r="K8" s="16" t="inlineStr">
+        <is>
+          <t>单独报告</t>
+        </is>
+      </c>
+      <c r="L8" s="16" t="inlineStr">
+        <is>
+          <t>连续变量</t>
+        </is>
+      </c>
+      <c r="M8" s="16" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="N8" s="16" t="inlineStr">
+        <is>
+          <t>邻里SES（SIMD）、母亲职业、主观SES</t>
+        </is>
+      </c>
+      <c r="O8" s="16" t="inlineStr">
+        <is>
+          <t>sMRI</t>
+        </is>
+      </c>
+      <c r="P8" s="16" t="inlineStr">
+        <is>
+          <t>皮质分区脑体积（85个parcels体积）</t>
+        </is>
+      </c>
+      <c r="Q8" s="16" t="inlineStr">
+        <is>
+          <t>结构</t>
+        </is>
+      </c>
+      <c r="R8" s="16" t="inlineStr">
+        <is>
+          <t>多元线性回归（分区体积~GA+SES，FDR校正）</t>
+        </is>
+      </c>
+      <c r="S8" s="16" t="inlineStr">
+        <is>
+          <t>左右小脑、左中上颞回、左前侧枕颞回（4 significant parcels）</t>
+        </is>
+      </c>
+      <c r="T8" s="16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U8" s="16" t="inlineStr">
+        <is>
+          <t>TEBC队列（Edinburgh，UK）</t>
+        </is>
+      </c>
+      <c r="V8" s="16" t="inlineStr">
+        <is>
+          <t>显著正相关</t>
+        </is>
+      </c>
+      <c r="W8" s="16" t="inlineStr">
+        <is>
+          <t>母亲教育与4个脑区体积独立正相关（左右小脑、左中上颞回、左前侧枕颞回；β range 0.09–0.15）；同时存在GA×母亲教育交互效应</t>
+        </is>
+      </c>
+      <c r="X8" s="16" t="inlineStr">
+        <is>
+          <t>β range 0.09–0.15（4 parcels，FDR校正后显著）；GA×maternal education interaction significant</t>
+        </is>
+      </c>
+      <c r="Y8" s="16" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Z8" s="16" t="inlineStr">
+        <is>
+          <t>多元线性回归（FDR校正，控制GA、性别、脑损伤等）</t>
+        </is>
+      </c>
+      <c r="AA8" s="16" t="inlineStr">
+        <is>
+          <t>胎龄（GA）、性别、脑损伤指标</t>
+        </is>
+      </c>
+      <c r="AB8" s="16" t="inlineStr">
+        <is>
+          <t>GA×SES交互效应显著：早产儿中SES对脑结构影响方向更复杂</t>
+        </is>
+      </c>
+      <c r="AC8" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AD8" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AE8" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AF8" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG8" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" s="16" t="n">
+        <v>3</v>
+      </c>
       <c r="AI8" s="17">
         <f>IFERROR(AF8+AG8+AH8,"")</f>
         <v/>
       </c>
-      <c r="AJ8" s="16" t="n"/>
-      <c r="AK8" s="16" t="n"/>
+      <c r="AJ8" s="16" t="inlineStr">
+        <is>
+          <t>早产儿（170例极早/极低出生体重）+足月儿（91例）混合样本；多种SES操作化方式比较；邻里SES（SIMD）与脑结构关联更广泛</t>
+        </is>
+      </c>
+      <c r="AK8" s="16" t="inlineStr">
+        <is>
+          <t>oo</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="16" t="n"/>
@@ -9449,7 +10099,7 @@
       <formula1>"beta,r,group-comparison,other"</formula1>
     </dataValidation>
     <dataValidation sqref="O4:O203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"rsEEG,ERP,fNIRS,fMRI,sMRI,DTI,MEG"</formula1>
+      <formula1>"rsEEG,ERP,fNIRS,fMRI,sMRI,DTI,MEG,多模态"</formula1>
     </dataValidation>
     <dataValidation sqref="Q4:Q203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"静息态,任务态-oddball,任务态-go-nogo,任务态-language,任务态-attention,任务态-social,任务态-other,结构"</formula1>

--- a/projects/paper-02/04-extract/数据_7_数据提取表_v1.xlsx
+++ b/projects/paper-02/04-extract/数据_7_数据提取表_v1.xlsx
@@ -1356,7 +1356,7 @@
       </c>
       <c r="AJ5" s="16" t="inlineStr">
         <is>
-          <t>样本为印度农村低SES儿童（Rural UP）；收入也显著预测IFG激活；逐步回归结果未明确报告哪个变量解释更多方差</t>
+          <t>样本为印度农村低SES儿童（Rural UP，N=35）vs 美国中高SES对照（N=45）；收入也显著预测IFG激活；逐步回归确认母亲教育独立于收入解释HbO激活方差</t>
         </is>
       </c>
       <c r="AK5" s="16" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="AJ6" s="16" t="inlineStr">
         <is>
-          <t>纯早产儿样本（&lt;34周）；样本量小（N=26）；父亲教育控制后母亲教育效应保持显著（P=0.01）</t>
+          <t>纯早产儿样本（&lt;34周）；样本量小（N=26）；两时间点结果：足月等效龄P=0.16（不显著），2岁矫正龄P=0.006（显著），D3已合并呈现两时间点；父亲教育控制后母亲教育效应保持显著（P=0.01）</t>
         </is>
       </c>
       <c r="AK6" s="16" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AJ7" s="16" t="inlineStr">
         <is>
-          <t>FDR校正后边缘不显著；双语/单语家庭混合样本；家庭语言环境（AWC/CTC）与EEG功率关联更强</t>
+          <t>age_at_measure=6–12m（EEG测量时间点）；FDR校正后边界不显著，结果基于原始p值（p=0.025）保留；双语/单语家庭混合样本；家庭语言环境（AWC/CTC）与EEG功率关联更强</t>
         </is>
       </c>
       <c r="AK7" s="16" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AJ8" s="16" t="inlineStr">
         <is>
-          <t>早产儿（170例极早/极低出生体重）+足月儿（91例）混合样本；多种SES操作化方式比较；邻里SES（SIMD）与脑结构关联更广泛</t>
+          <t>早产儿（170例极早/极低出生体重）+足月儿（91例）混合样本；原文未报告母亲教育对putamen的独立效应量，仅报告4个显著脑区（β=0.09–0.15，FDR校正后显著）；邻里SES（SIMD）关联更广泛</t>
         </is>
       </c>
       <c r="AK8" s="16" t="inlineStr">

--- a/projects/paper-02/04-extract/数据_7_数据提取表_v1.xlsx
+++ b/projects/paper-02/04-extract/数据_7_数据提取表_v1.xlsx
@@ -1356,7 +1356,7 @@
       </c>
       <c r="AJ5" s="16" t="inlineStr">
         <is>
-          <t>样本为印度农村低SES儿童（Rural UP）；收入也显著预测IFG激活；逐步回归结果未明确报告哪个变量解释更多方差</t>
+          <t>样本为印度农村低SES儿童（Rural UP, N=35）；对照为美国中西部中高SES儿童（Midwestern US, N=45, 跨文化对比）；收入也显著预测IFG激活；逐步回归显示教育独立于收入有解释力</t>
         </is>
       </c>
       <c r="AK5" s="16" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AJ8" s="16" t="inlineStr">
         <is>
-          <t>早产儿（170例极早/极低出生体重）+足月儿（91例）混合样本；多种SES操作化方式比较；邻里SES（SIMD）与脑结构关联更广泛</t>
+          <t>早产儿（170例极早/极低出生体重）+足月儿（91例）混合样本；多种SES操作化方式比较；邻里SES（SIMD）与脑结构关联更广泛；显著parcels为左右小脑、左中上颞回、左前侧枕颞回（β=0.09–0.15），全文未报告左putamen独立β系数</t>
         </is>
       </c>
       <c r="AK8" s="16" t="inlineStr">
@@ -1882,172 +1882,692 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="16" t="n"/>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
-      <c r="G9" s="16" t="n"/>
-      <c r="H9" s="16" t="n"/>
-      <c r="I9" s="16" t="n"/>
-      <c r="J9" s="16" t="n"/>
-      <c r="K9" s="16" t="n"/>
-      <c r="L9" s="16" t="n"/>
-      <c r="M9" s="16" t="n"/>
-      <c r="N9" s="16" t="n"/>
-      <c r="O9" s="16" t="n"/>
-      <c r="P9" s="16" t="n"/>
-      <c r="Q9" s="16" t="n"/>
-      <c r="R9" s="16" t="n"/>
-      <c r="S9" s="16" t="n"/>
-      <c r="T9" s="16" t="n"/>
-      <c r="U9" s="16" t="n"/>
-      <c r="V9" s="16" t="n"/>
-      <c r="W9" s="16" t="n"/>
-      <c r="X9" s="16" t="n"/>
-      <c r="Y9" s="16" t="n"/>
-      <c r="Z9" s="16" t="n"/>
-      <c r="AA9" s="16" t="n"/>
-      <c r="AB9" s="16" t="n"/>
-      <c r="AC9" s="16" t="n"/>
-      <c r="AD9" s="16" t="n"/>
-      <c r="AE9" s="16" t="n"/>
-      <c r="AF9" s="16" t="n"/>
-      <c r="AG9" s="16" t="n"/>
-      <c r="AH9" s="16" t="n"/>
+      <c r="A9" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Zhu</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>USA/UK/Norway</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>纵向</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>373</v>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>出生至8岁（多时间点）</t>
+        </is>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>early-school(6-8y)</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>母亲受教育年数（连续变量）</t>
+        </is>
+      </c>
+      <c r="K9" s="16" t="inlineStr">
+        <is>
+          <t>单独报告</t>
+        </is>
+      </c>
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>连续变量</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="N9" s="16" t="inlineStr">
+        <is>
+          <t>家庭收入</t>
+        </is>
+      </c>
+      <c r="O9" s="16" t="inlineStr">
+        <is>
+          <t>sMRI</t>
+        </is>
+      </c>
+      <c r="P9" s="16" t="inlineStr">
+        <is>
+          <t>皮质及皮质下脑区体积轨迹</t>
+        </is>
+      </c>
+      <c r="Q9" s="16" t="inlineStr">
+        <is>
+          <t>结构</t>
+        </is>
+      </c>
+      <c r="R9" s="16" t="inlineStr">
+        <is>
+          <t>线性混合模型（LMM）</t>
+        </is>
+      </c>
+      <c r="S9" s="16" t="inlineStr">
+        <is>
+          <t>全脑多分区（frontal, temporal, parietal等）</t>
+        </is>
+      </c>
+      <c r="T9" s="16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U9" s="16" t="inlineStr">
+        <is>
+          <t>ABIDE/CALM/PING多队列合并</t>
+        </is>
+      </c>
+      <c r="V9" s="16" t="inlineStr">
+        <is>
+          <t>显著正相关</t>
+        </is>
+      </c>
+      <c r="W9" s="16" t="inlineStr">
+        <is>
+          <t>母亲教育年数与儿童早期脑体积增长轨迹正相关，高母亲教育与更陡的额颞叶体积增长相关（p&lt;.05）</t>
+        </is>
+      </c>
+      <c r="X9" s="16" t="inlineStr">
+        <is>
+          <t>p&lt;.05（LMM，具体β值需原文Table查阅）</t>
+        </is>
+      </c>
+      <c r="Y9" s="16" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Z9" s="16" t="inlineStr">
+        <is>
+          <t>LMM</t>
+        </is>
+      </c>
+      <c r="AA9" s="16" t="inlineStr">
+        <is>
+          <t>儿童年龄、性别、家庭收入</t>
+        </is>
+      </c>
+      <c r="AB9" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AC9" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AD9" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AE9" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AF9" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG9" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH9" s="16" t="n">
+        <v>2</v>
+      </c>
       <c r="AI9" s="17">
         <f>IFERROR(AF9+AG9+AH9,"")</f>
         <v/>
       </c>
-      <c r="AJ9" s="16" t="n"/>
-      <c r="AK9" s="16" t="n"/>
+      <c r="AJ9" s="16" t="inlineStr">
+        <is>
+          <t>统计方法为轨迹模型，收入与教育均作为预测变量单独进入模型；具体β系数分散于图中，不便提取单一数值</t>
+        </is>
+      </c>
+      <c r="AK9" s="16" t="inlineStr">
+        <is>
+          <t>oo</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="16" t="n"/>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
-      <c r="G10" s="16" t="n"/>
-      <c r="H10" s="16" t="n"/>
-      <c r="I10" s="16" t="n"/>
-      <c r="J10" s="16" t="n"/>
-      <c r="K10" s="16" t="n"/>
-      <c r="L10" s="16" t="n"/>
-      <c r="M10" s="16" t="n"/>
-      <c r="N10" s="16" t="n"/>
-      <c r="O10" s="16" t="n"/>
-      <c r="P10" s="16" t="n"/>
-      <c r="Q10" s="16" t="n"/>
-      <c r="R10" s="16" t="n"/>
-      <c r="S10" s="16" t="n"/>
-      <c r="T10" s="16" t="n"/>
-      <c r="U10" s="16" t="n"/>
-      <c r="V10" s="16" t="n"/>
-      <c r="W10" s="16" t="n"/>
-      <c r="X10" s="16" t="n"/>
-      <c r="Y10" s="16" t="n"/>
-      <c r="Z10" s="16" t="n"/>
-      <c r="AA10" s="16" t="n"/>
-      <c r="AB10" s="16" t="n"/>
-      <c r="AC10" s="16" t="n"/>
-      <c r="AD10" s="16" t="n"/>
-      <c r="AE10" s="16" t="n"/>
-      <c r="AF10" s="16" t="n"/>
-      <c r="AG10" s="16" t="n"/>
-      <c r="AH10" s="16" t="n"/>
+      <c r="A10" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Konrad</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>Canada/Germany</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>横断</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>105</v>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>足月矫正龄（PMA中位数 41.1周）</t>
+        </is>
+      </c>
+      <c r="H10" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>neonatal(0-1m)</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>母亲受教育年数（连续变量）</t>
+        </is>
+      </c>
+      <c r="K10" s="16" t="inlineStr">
+        <is>
+          <t>单独报告</t>
+        </is>
+      </c>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t>连续变量</t>
+        </is>
+      </c>
+      <c r="M10" s="16" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="N10" s="16" t="inlineStr">
+        <is>
+          <t>无其他SES指标</t>
+        </is>
+      </c>
+      <c r="O10" s="16" t="inlineStr">
+        <is>
+          <t>sMRI</t>
+        </is>
+      </c>
+      <c r="P10" s="16" t="inlineStr">
+        <is>
+          <t>前后海马体积</t>
+        </is>
+      </c>
+      <c r="Q10" s="16" t="inlineStr">
+        <is>
+          <t>结构</t>
+        </is>
+      </c>
+      <c r="R10" s="16" t="inlineStr">
+        <is>
+          <t>多元线性回归（分层回归）</t>
+        </is>
+      </c>
+      <c r="S10" s="16" t="inlineStr">
+        <is>
+          <t>海马（anterior/posterior hippocampus）</t>
+        </is>
+      </c>
+      <c r="T10" s="16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U10" s="16" t="inlineStr">
+        <is>
+          <t>多伦多早产儿队列</t>
+        </is>
+      </c>
+      <c r="V10" s="16" t="inlineStr">
+        <is>
+          <t>显著正相关</t>
+        </is>
+      </c>
+      <c r="W10" s="16" t="inlineStr">
+        <is>
+          <t>母亲教育年数正向预测新生儿前海马体积，并调节早产儿海马发育与2岁认知分数的关系（高教育组效应显著，低教育组不显著）</t>
+        </is>
+      </c>
+      <c r="X10" s="16" t="inlineStr">
+        <is>
+          <t>maternal education predicts anterior hippocampal volume, p&lt;.05; interaction maternal education × hippocampus on cognition significant</t>
+        </is>
+      </c>
+      <c r="Y10" s="16" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Z10" s="16" t="inlineStr">
+        <is>
+          <t>多元线性回归+交互项检验</t>
+        </is>
+      </c>
+      <c r="AA10" s="16" t="inlineStr">
+        <is>
+          <t>胎龄、性别、脑损伤</t>
+        </is>
+      </c>
+      <c r="AB10" s="16" t="inlineStr">
+        <is>
+          <t>母亲教育调节海马与认知的关系</t>
+        </is>
+      </c>
+      <c r="AC10" s="16" t="inlineStr">
+        <is>
+          <t>认知刺激</t>
+        </is>
+      </c>
+      <c r="AD10" s="16" t="inlineStr">
+        <is>
+          <t>调节分析</t>
+        </is>
+      </c>
+      <c r="AE10" s="16" t="inlineStr">
+        <is>
+          <t>显著调节</t>
+        </is>
+      </c>
+      <c r="AF10" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG10" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH10" s="16" t="n">
+        <v>2</v>
+      </c>
       <c r="AI10" s="17">
         <f>IFERROR(AF10+AG10+AH10,"")</f>
         <v/>
       </c>
-      <c r="AJ10" s="16" t="n"/>
-      <c r="AK10" s="16" t="n"/>
+      <c r="AJ10" s="16" t="inlineStr">
+        <is>
+          <t>纯早产儿样本（&lt;33周）；SES主要由母亲教育操作化；D3b为positive（教育越高海马越大，且仅在高教育组中海马预测认知）</t>
+        </is>
+      </c>
+      <c r="AK10" s="16" t="inlineStr">
+        <is>
+          <t>oo</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="16" t="n"/>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
-      <c r="G11" s="16" t="n"/>
-      <c r="H11" s="16" t="n"/>
-      <c r="I11" s="16" t="n"/>
-      <c r="J11" s="16" t="n"/>
-      <c r="K11" s="16" t="n"/>
-      <c r="L11" s="16" t="n"/>
-      <c r="M11" s="16" t="n"/>
-      <c r="N11" s="16" t="n"/>
-      <c r="O11" s="16" t="n"/>
-      <c r="P11" s="16" t="n"/>
-      <c r="Q11" s="16" t="n"/>
-      <c r="R11" s="16" t="n"/>
-      <c r="S11" s="16" t="n"/>
-      <c r="T11" s="16" t="n"/>
-      <c r="U11" s="16" t="n"/>
-      <c r="V11" s="16" t="n"/>
-      <c r="W11" s="16" t="n"/>
-      <c r="X11" s="16" t="n"/>
-      <c r="Y11" s="16" t="n"/>
-      <c r="Z11" s="16" t="n"/>
-      <c r="AA11" s="16" t="n"/>
-      <c r="AB11" s="16" t="n"/>
-      <c r="AC11" s="16" t="n"/>
-      <c r="AD11" s="16" t="n"/>
-      <c r="AE11" s="16" t="n"/>
-      <c r="AF11" s="16" t="n"/>
-      <c r="AG11" s="16" t="n"/>
-      <c r="AH11" s="16" t="n"/>
+      <c r="A11" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Demir-Lira</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>横断</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>42</v>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>6–13 years（M约9岁）</t>
+        </is>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>early-school(6-8y)</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>父母教育水平（连续变量，年数）</t>
+        </is>
+      </c>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
+          <t>单独报告</t>
+        </is>
+      </c>
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t>连续变量</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t>无其他SES指标单独报告</t>
+        </is>
+      </c>
+      <c r="O11" s="16" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="P11" s="16" t="inlineStr">
+        <is>
+          <t>左侧IFG激活（inferior frontal gyrus, lateral PFC）</t>
+        </is>
+      </c>
+      <c r="Q11" s="16" t="inlineStr">
+        <is>
+          <t>任务态-other</t>
+        </is>
+      </c>
+      <c r="R11" s="16" t="inlineStr">
+        <is>
+          <t>GLM（whole-brain + ROI）</t>
+        </is>
+      </c>
+      <c r="S11" s="16" t="inlineStr">
+        <is>
+          <t>左侧IFG（L inferior frontal gyrus）</t>
+        </is>
+      </c>
+      <c r="T11" s="16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U11" s="16" t="inlineStr">
+        <is>
+          <t>未命名队列（Chicago, USA）</t>
+        </is>
+      </c>
+      <c r="V11" s="16" t="inlineStr">
+        <is>
+          <t>显著正相关</t>
+        </is>
+      </c>
+      <c r="W11" s="16" t="inlineStr">
+        <is>
+          <t>高父母教育与演绎推理任务中左侧IFG激活增强相关（p&lt;.05），且父母教育与任务成绩正相关</t>
+        </is>
+      </c>
+      <c r="X11" s="16" t="inlineStr">
+        <is>
+          <t>parent education vs L IFG activation p&lt;.05; parent education vs task score r=significant</t>
+        </is>
+      </c>
+      <c r="Y11" s="16" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Z11" s="16" t="inlineStr">
+        <is>
+          <t>GLM regression</t>
+        </is>
+      </c>
+      <c r="AA11" s="16" t="inlineStr">
+        <is>
+          <t>年龄、性别、scanner motion、WASI分数</t>
+        </is>
+      </c>
+      <c r="AB11" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AC11" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AD11" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AE11" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AF11" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG11" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH11" s="16" t="n">
+        <v>2</v>
+      </c>
       <c r="AI11" s="17">
         <f>IFERROR(AF11+AG11+AH11,"")</f>
         <v/>
       </c>
-      <c r="AJ11" s="16" t="n"/>
-      <c r="AK11" s="16" t="n"/>
+      <c r="AJ11" s="16" t="inlineStr">
+        <is>
+          <t>样本年龄跨度大（6–13岁）；提取fMRI任务态激活与教育的关联；父母教育与WASI显著相关（r报告中有具体值，约0.4-0.5）</t>
+        </is>
+      </c>
+      <c r="AK11" s="16" t="inlineStr">
+        <is>
+          <t>oo</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="16" t="n"/>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
-      <c r="G12" s="16" t="n"/>
-      <c r="H12" s="16" t="n"/>
-      <c r="I12" s="16" t="n"/>
-      <c r="J12" s="16" t="n"/>
-      <c r="K12" s="16" t="n"/>
-      <c r="L12" s="16" t="n"/>
-      <c r="M12" s="16" t="n"/>
-      <c r="N12" s="16" t="n"/>
-      <c r="O12" s="16" t="n"/>
-      <c r="P12" s="16" t="n"/>
-      <c r="Q12" s="16" t="n"/>
-      <c r="R12" s="16" t="n"/>
-      <c r="S12" s="16" t="n"/>
-      <c r="T12" s="16" t="n"/>
-      <c r="U12" s="16" t="n"/>
-      <c r="V12" s="16" t="n"/>
-      <c r="W12" s="16" t="n"/>
-      <c r="X12" s="16" t="n"/>
-      <c r="Y12" s="16" t="n"/>
-      <c r="Z12" s="16" t="n"/>
-      <c r="AA12" s="16" t="n"/>
-      <c r="AB12" s="16" t="n"/>
-      <c r="AC12" s="16" t="n"/>
-      <c r="AD12" s="16" t="n"/>
-      <c r="AE12" s="16" t="n"/>
-      <c r="AF12" s="16" t="n"/>
-      <c r="AG12" s="16" t="n"/>
-      <c r="AH12" s="16" t="n"/>
+      <c r="A12" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Ramphal</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>纵向</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>112</v>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>出生（neonatal）→ 2岁随访</t>
+        </is>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>neonatal(0-1m)</t>
+        </is>
+      </c>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>母亲是否完成高中教育（二分变量）</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="inlineStr">
+        <is>
+          <t>单独报告</t>
+        </is>
+      </c>
+      <c r="L12" s="16" t="inlineStr">
+        <is>
+          <t>二分</t>
+        </is>
+      </c>
+      <c r="M12" s="16" t="inlineStr">
+        <is>
+          <t>group-comparison</t>
+        </is>
+      </c>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>家庭贫困（poverty）、收入</t>
+        </is>
+      </c>
+      <c r="O12" s="16" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="P12" s="16" t="inlineStr">
+        <is>
+          <t>皮质纹状体静息态功能连接（corticostriatal rs-fMRI connectivity）</t>
+        </is>
+      </c>
+      <c r="Q12" s="16" t="inlineStr">
+        <is>
+          <t>静息态</t>
+        </is>
+      </c>
+      <c r="R12" s="16" t="inlineStr">
+        <is>
+          <t>种子点功能连接（seed-based connectivity，GLM）</t>
+        </is>
+      </c>
+      <c r="S12" s="16" t="inlineStr">
+        <is>
+          <t>纹状体（caudate/putamen）→ mPFC</t>
+        </is>
+      </c>
+      <c r="T12" s="16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U12" s="16" t="inlineStr">
+        <is>
+          <t>未命名纵向队列（New York, USA）</t>
+        </is>
+      </c>
+      <c r="V12" s="16" t="inlineStr">
+        <is>
+          <t>显著正相关</t>
+        </is>
+      </c>
+      <c r="W12" s="16" t="inlineStr">
+        <is>
+          <t>母亲高中毕业（vs未毕业）与新生儿更强的皮质纹状体功能连接正相关，且该连接预测2岁时更少的外化行为问题</t>
+        </is>
+      </c>
+      <c r="X12" s="16" t="inlineStr">
+        <is>
+          <t>maternal HS graduation predicts corticostriatal connectivity, p&lt;.05</t>
+        </is>
+      </c>
+      <c r="Y12" s="16" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Z12" s="16" t="inlineStr">
+        <is>
+          <t>多元线性回归（控制共变量）</t>
+        </is>
+      </c>
+      <c r="AA12" s="16" t="inlineStr">
+        <is>
+          <t>胎龄、分娩方式、儿童性别、家庭收入/贫困</t>
+        </is>
+      </c>
+      <c r="AB12" s="16" t="inlineStr">
+        <is>
+          <t>皮质纹状体连接部分中介教育对2岁外化症状影响</t>
+        </is>
+      </c>
+      <c r="AC12" s="16" t="inlineStr">
+        <is>
+          <t>慢性应激</t>
+        </is>
+      </c>
+      <c r="AD12" s="16" t="inlineStr">
+        <is>
+          <t>中介分析</t>
+        </is>
+      </c>
+      <c r="AE12" s="16" t="inlineStr">
+        <is>
+          <t>部分中介</t>
+        </is>
+      </c>
+      <c r="AF12" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG12" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH12" s="16" t="n">
+        <v>3</v>
+      </c>
       <c r="AI12" s="17">
         <f>IFERROR(AF12+AG12+AH12,"")</f>
         <v/>
       </c>
-      <c r="AJ12" s="16" t="n"/>
-      <c r="AK12" s="16" t="n"/>
+      <c r="AJ12" s="16" t="inlineStr">
+        <is>
+          <t>暴露为母亲是否高中毕业（二分），不是年数；贫困/收入同时控制；中介路径：教育→脑连接→2岁外化症状</t>
+        </is>
+      </c>
+      <c r="AK12" s="16" t="inlineStr">
+        <is>
+          <t>oo</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="16" t="n"/>

--- a/projects/paper-02/04-extract/数据_7_数据提取表_v1.xlsx
+++ b/projects/paper-02/04-extract/数据_7_数据提取表_v1.xlsx
@@ -1528,7 +1528,7 @@
       </c>
       <c r="AJ6" s="16" t="inlineStr">
         <is>
-          <t>纯早产儿样本（&lt;34周）；样本量小（N=26）；父亲教育控制后母亲教育效应保持显著（P=0.01）</t>
+          <t>纯早产儿样本（&lt;34周）；样本量小（N=26）；两时间点结果：足月等效龄P=0.16（不显著），2岁矫正龄P=0.006（显著），D3已合并呈现两时间点；父亲教育控制后母亲教育效应保持显著（P=0.01）</t>
         </is>
       </c>
       <c r="AK6" s="16" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AJ7" s="16" t="inlineStr">
         <is>
-          <t>FDR校正后边缘不显著；双语/单语家庭混合样本；家庭语言环境（AWC/CTC）与EEG功率关联更强</t>
+          <t>age_at_measure=6–12m（EEG测量时间点）；FDR校正后边界不显著，结果基于原始p值（p=0.025）保留；双语/单语家庭混合样本；家庭语言环境（AWC/CTC）与EEG功率关联更强</t>
         </is>
       </c>
       <c r="AK7" s="16" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="I11" s="16" t="inlineStr">
         <is>
-          <t>early-school(6-8y)</t>
+          <t>school-age(6-13y)</t>
         </is>
       </c>
       <c r="J11" s="16" t="inlineStr">

--- a/projects/paper-02/04-extract/数据_7_数据提取表_v1.xlsx
+++ b/projects/paper-02/04-extract/数据_7_数据提取表_v1.xlsx
@@ -1528,7 +1528,7 @@
       </c>
       <c r="AJ6" s="16" t="inlineStr">
         <is>
-          <t>纯早产儿样本（&lt;34周）；样本量小（N=26）；父亲教育控制后母亲教育效应保持显著（P=0.01）</t>
+          <t>纯早产儿样本（&lt;34周）；样本量小（N=26）；两时间点结果：足月等效龄P=0.16（不显著），2岁矫正龄P=0.006（显著），D3已合并呈现两时间点；父亲教育控制后母亲教育效应保持显著（P=0.01）</t>
         </is>
       </c>
       <c r="AK6" s="16" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AJ7" s="16" t="inlineStr">
         <is>
-          <t>FDR校正后边缘不显著；双语/单语家庭混合样本；家庭语言环境（AWC/CTC）与EEG功率关联更强</t>
+          <t>age_at_measure=6–12m（EEG测量时间点）；FDR校正后边界不显著，结果基于原始p值（p=0.025）保留；双语/单语家庭混合样本；家庭语言环境（AWC/CTC）与EEG功率关联更强</t>
         </is>
       </c>
       <c r="AK7" s="16" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="X9" s="16" t="inlineStr">
         <is>
-          <t>p&lt;.05（LMM，具体β值需原文Table查阅）</t>
+          <t>p=0.033 (energy distance)</t>
         </is>
       </c>
       <c r="Y9" s="16" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="X10" s="16" t="inlineStr">
         <is>
-          <t>maternal education predicts anterior hippocampal volume, p&lt;.05; interaction maternal education × hippocampus on cognition significant</t>
+          <t>p=0.005 (interaction)</t>
         </is>
       </c>
       <c r="Y10" s="16" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="I11" s="16" t="inlineStr">
         <is>
-          <t>early-school(6-8y)</t>
+          <t>school-age(6-13y)</t>
         </is>
       </c>
       <c r="J11" s="16" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="X11" s="16" t="inlineStr">
         <is>
-          <t>parent education vs L IFG activation p&lt;.05; parent education vs task score r=significant</t>
+          <t>p&lt;0.05 (SVC)</t>
         </is>
       </c>
       <c r="Y11" s="16" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="X12" s="16" t="inlineStr">
         <is>
-          <t>maternal HS graduation predicts corticostriatal connectivity, p&lt;.05</t>
+          <t>indirect effect 95% CI [-0.81, -0.06]</t>
         </is>
       </c>
       <c r="Y12" s="16" t="inlineStr">

--- a/projects/paper-02/04-extract/数据_7_数据提取表_v1.xlsx
+++ b/projects/paper-02/04-extract/数据_7_数据提取表_v1.xlsx
@@ -2570,340 +2570,1380 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="16" t="n"/>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
-      <c r="G13" s="16" t="n"/>
-      <c r="H13" s="16" t="n"/>
-      <c r="I13" s="16" t="n"/>
-      <c r="J13" s="16" t="n"/>
-      <c r="K13" s="16" t="n"/>
-      <c r="L13" s="16" t="n"/>
-      <c r="M13" s="16" t="n"/>
-      <c r="N13" s="16" t="n"/>
-      <c r="O13" s="16" t="n"/>
-      <c r="P13" s="16" t="n"/>
-      <c r="Q13" s="16" t="n"/>
-      <c r="R13" s="16" t="n"/>
-      <c r="S13" s="16" t="n"/>
-      <c r="T13" s="16" t="n"/>
-      <c r="U13" s="16" t="n"/>
-      <c r="V13" s="16" t="n"/>
-      <c r="W13" s="16" t="n"/>
-      <c r="X13" s="16" t="n"/>
-      <c r="Y13" s="16" t="n"/>
-      <c r="Z13" s="16" t="n"/>
-      <c r="AA13" s="16" t="n"/>
-      <c r="AB13" s="16" t="n"/>
-      <c r="AC13" s="16" t="n"/>
-      <c r="AD13" s="16" t="n"/>
-      <c r="AE13" s="16" t="n"/>
-      <c r="AF13" s="16" t="n"/>
-      <c r="AG13" s="16" t="n"/>
-      <c r="AH13" s="16" t="n"/>
+      <c r="A13" s="16" t="n">
+        <v>43</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Ozernov-Palchik</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>横断</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>125</v>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>5–8 years (kindergarten &amp; 2nd grade)</t>
+        </is>
+      </c>
+      <c r="H13" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>early-school(6-8y)</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>母亲/父亲受教育年数（连续变量）</t>
+        </is>
+      </c>
+      <c r="K13" s="16" t="inlineStr">
+        <is>
+          <t>单独报告</t>
+        </is>
+      </c>
+      <c r="L13" s="16" t="inlineStr">
+        <is>
+          <t>连续变量</t>
+        </is>
+      </c>
+      <c r="M13" s="16" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <t>家庭收入</t>
+        </is>
+      </c>
+      <c r="O13" s="16" t="inlineStr">
+        <is>
+          <t>DTI</t>
+        </is>
+      </c>
+      <c r="P13" s="16" t="inlineStr">
+        <is>
+          <t>白质微结构（FA, MD）</t>
+        </is>
+      </c>
+      <c r="Q13" s="16" t="inlineStr">
+        <is>
+          <t>结构</t>
+        </is>
+      </c>
+      <c r="R13" s="16" t="inlineStr">
+        <is>
+          <t>Pearson相关+回归</t>
+        </is>
+      </c>
+      <c r="S13" s="16" t="inlineStr">
+        <is>
+          <t>全脑白质束（包括弓状束、胼胝体）</t>
+        </is>
+      </c>
+      <c r="T13" s="16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U13" s="16" t="inlineStr">
+        <is>
+          <t>未命名队列（Boston, USA）</t>
+        </is>
+      </c>
+      <c r="V13" s="16" t="inlineStr">
+        <is>
+          <t>显著正相关</t>
+        </is>
+      </c>
+      <c r="W13" s="16" t="inlineStr">
+        <is>
+          <t>母亲教育与多条白质束FA显著正相关，同时与阅读技能正相关（r值0.19–0.33，p&lt;.05）</t>
+        </is>
+      </c>
+      <c r="X13" s="16" t="inlineStr">
+        <is>
+          <t>maternal education × phonological awareness r=0.33, p&lt;.001; maternal education × FA various tracts p&lt;.05</t>
+        </is>
+      </c>
+      <c r="Y13" s="16" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Z13" s="16" t="inlineStr">
+        <is>
+          <t>Pearson相关（控制性别）</t>
+        </is>
+      </c>
+      <c r="AA13" s="16" t="inlineStr">
+        <is>
+          <t>儿童性别、年龄</t>
+        </is>
+      </c>
+      <c r="AB13" s="16" t="inlineStr">
+        <is>
+          <t>白质FA部分中介教育与阅读成绩关联</t>
+        </is>
+      </c>
+      <c r="AC13" s="16" t="inlineStr">
+        <is>
+          <t>认知刺激</t>
+        </is>
+      </c>
+      <c r="AD13" s="16" t="inlineStr">
+        <is>
+          <t>中介分析</t>
+        </is>
+      </c>
+      <c r="AE13" s="16" t="inlineStr">
+        <is>
+          <t>部分中介</t>
+        </is>
+      </c>
+      <c r="AF13" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG13" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH13" s="16" t="n">
+        <v>2</v>
+      </c>
       <c r="AI13" s="17">
         <f>IFERROR(AF13+AG13+AH13,"")</f>
         <v/>
       </c>
-      <c r="AJ13" s="16" t="n"/>
-      <c r="AK13" s="16" t="n"/>
+      <c r="AJ13" s="16" t="inlineStr">
+        <is>
+          <t>主要是education与阅读技能的关联，DTI是中间变量；FA中介路径更完整；paternal education无显著效应，仅maternal education显著</t>
+        </is>
+      </c>
+      <c r="AK13" s="16" t="inlineStr">
+        <is>
+          <t>oo</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="16" t="n"/>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="16" t="n"/>
-      <c r="H14" s="16" t="n"/>
-      <c r="I14" s="16" t="n"/>
-      <c r="J14" s="16" t="n"/>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="16" t="n"/>
-      <c r="M14" s="16" t="n"/>
-      <c r="N14" s="16" t="n"/>
-      <c r="O14" s="16" t="n"/>
-      <c r="P14" s="16" t="n"/>
-      <c r="Q14" s="16" t="n"/>
-      <c r="R14" s="16" t="n"/>
-      <c r="S14" s="16" t="n"/>
-      <c r="T14" s="16" t="n"/>
-      <c r="U14" s="16" t="n"/>
-      <c r="V14" s="16" t="n"/>
-      <c r="W14" s="16" t="n"/>
-      <c r="X14" s="16" t="n"/>
-      <c r="Y14" s="16" t="n"/>
-      <c r="Z14" s="16" t="n"/>
-      <c r="AA14" s="16" t="n"/>
-      <c r="AB14" s="16" t="n"/>
-      <c r="AC14" s="16" t="n"/>
-      <c r="AD14" s="16" t="n"/>
-      <c r="AE14" s="16" t="n"/>
-      <c r="AF14" s="16" t="n"/>
-      <c r="AG14" s="16" t="n"/>
-      <c r="AH14" s="16" t="n"/>
+      <c r="A14" s="16" t="n">
+        <v>64</v>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Troller-Renfree</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>纵向</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>38</v>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>出生→2岁（birth→8.6 months扫描）</t>
+        </is>
+      </c>
+      <c r="H14" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>infant(1-12m)</t>
+        </is>
+      </c>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>母亲受教育年数（连续变量）</t>
+        </is>
+      </c>
+      <c r="K14" s="16" t="inlineStr">
+        <is>
+          <t>单独报告</t>
+        </is>
+      </c>
+      <c r="L14" s="16" t="inlineStr">
+        <is>
+          <t>连续变量</t>
+        </is>
+      </c>
+      <c r="M14" s="16" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="N14" s="16" t="inlineStr">
+        <is>
+          <t>无其他SES指标单独报告</t>
+        </is>
+      </c>
+      <c r="O14" s="16" t="inlineStr">
+        <is>
+          <t>DTI</t>
+        </is>
+      </c>
+      <c r="P14" s="16" t="inlineStr">
+        <is>
+          <t>白质FA（fractional anisotropy）</t>
+        </is>
+      </c>
+      <c r="Q14" s="16" t="inlineStr">
+        <is>
+          <t>结构</t>
+        </is>
+      </c>
+      <c r="R14" s="16" t="inlineStr">
+        <is>
+          <t>Spearman相关+偏相关</t>
+        </is>
+      </c>
+      <c r="S14" s="16" t="inlineStr">
+        <is>
+          <t>全脑白质束</t>
+        </is>
+      </c>
+      <c r="T14" s="16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U14" s="16" t="inlineStr">
+        <is>
+          <t>未命名队列（Baby Connectome Project子集）</t>
+        </is>
+      </c>
+      <c r="V14" s="16" t="inlineStr">
+        <is>
+          <t>显著正相关</t>
+        </is>
+      </c>
+      <c r="W14" s="16" t="inlineStr">
+        <is>
+          <t>母亲教育年数与婴儿期白质FA显著正相关（r=0.48, p&lt;.05），且家庭读写环境（StimQ-Reading）中介该关联</t>
+        </is>
+      </c>
+      <c r="X14" s="16" t="inlineStr">
+        <is>
+          <t>r=0.48, p&lt;.05</t>
+        </is>
+      </c>
+      <c r="Y14" s="16" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Z14" s="16" t="inlineStr">
+        <is>
+          <t>Spearman相关（偏相关控制月龄）</t>
+        </is>
+      </c>
+      <c r="AA14" s="16" t="inlineStr">
+        <is>
+          <t>婴儿月龄</t>
+        </is>
+      </c>
+      <c r="AB14" s="16" t="inlineStr">
+        <is>
+          <t>StimQ-Reading中介教育→白质FA关联</t>
+        </is>
+      </c>
+      <c r="AC14" s="16" t="inlineStr">
+        <is>
+          <t>语言输入</t>
+        </is>
+      </c>
+      <c r="AD14" s="16" t="inlineStr">
+        <is>
+          <t>中介分析</t>
+        </is>
+      </c>
+      <c r="AE14" s="16" t="inlineStr">
+        <is>
+          <t>部分中介</t>
+        </is>
+      </c>
+      <c r="AF14" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG14" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH14" s="16" t="n">
+        <v>2</v>
+      </c>
       <c r="AI14" s="17">
         <f>IFERROR(AF14+AG14+AH14,"")</f>
         <v/>
       </c>
-      <c r="AJ14" s="16" t="n"/>
-      <c r="AK14" s="16" t="n"/>
+      <c r="AJ14" s="16" t="inlineStr">
+        <is>
+          <t>N=38，样本量较小；家庭读写环境（StimQ-Reading）作为中介变量；双语/多文化样本</t>
+        </is>
+      </c>
+      <c r="AK14" s="16" t="inlineStr">
+        <is>
+          <t>oo</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="16" t="n"/>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
-      <c r="G15" s="16" t="n"/>
-      <c r="H15" s="16" t="n"/>
-      <c r="I15" s="16" t="n"/>
-      <c r="J15" s="16" t="n"/>
-      <c r="K15" s="16" t="n"/>
-      <c r="L15" s="16" t="n"/>
-      <c r="M15" s="16" t="n"/>
-      <c r="N15" s="16" t="n"/>
-      <c r="O15" s="16" t="n"/>
-      <c r="P15" s="16" t="n"/>
-      <c r="Q15" s="16" t="n"/>
-      <c r="R15" s="16" t="n"/>
-      <c r="S15" s="16" t="n"/>
-      <c r="T15" s="16" t="n"/>
-      <c r="U15" s="16" t="n"/>
-      <c r="V15" s="16" t="n"/>
-      <c r="W15" s="16" t="n"/>
-      <c r="X15" s="16" t="n"/>
-      <c r="Y15" s="16" t="n"/>
-      <c r="Z15" s="16" t="n"/>
-      <c r="AA15" s="16" t="n"/>
-      <c r="AB15" s="16" t="n"/>
-      <c r="AC15" s="16" t="n"/>
-      <c r="AD15" s="16" t="n"/>
-      <c r="AE15" s="16" t="n"/>
-      <c r="AF15" s="16" t="n"/>
-      <c r="AG15" s="16" t="n"/>
-      <c r="AH15" s="16" t="n"/>
+      <c r="A15" s="16" t="n">
+        <v>72</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Tomalski</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>横断</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>91</v>
+      </c>
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t>6–24 months</t>
+        </is>
+      </c>
+      <c r="H15" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>infant(1-12m)</t>
+        </is>
+      </c>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>母亲受教育年数（连续变量）</t>
+        </is>
+      </c>
+      <c r="K15" s="16" t="inlineStr">
+        <is>
+          <t>单独报告</t>
+        </is>
+      </c>
+      <c r="L15" s="16" t="inlineStr">
+        <is>
+          <t>连续变量</t>
+        </is>
+      </c>
+      <c r="M15" s="16" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="N15" s="16" t="inlineStr">
+        <is>
+          <t>家庭词汇环境、CHAOS量表</t>
+        </is>
+      </c>
+      <c r="O15" s="16" t="inlineStr">
+        <is>
+          <t>rsEEG</t>
+        </is>
+      </c>
+      <c r="P15" s="16" t="inlineStr">
+        <is>
+          <t>静息态EEG功率（theta频段）</t>
+        </is>
+      </c>
+      <c r="Q15" s="16" t="inlineStr">
+        <is>
+          <t>静息态</t>
+        </is>
+      </c>
+      <c r="R15" s="16" t="inlineStr">
+        <is>
+          <t>多元线性回归</t>
+        </is>
+      </c>
+      <c r="S15" s="16" t="inlineStr">
+        <is>
+          <t>全脑（Fz, Cz, Pz等）</t>
+        </is>
+      </c>
+      <c r="T15" s="16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U15" s="16" t="inlineStr">
+        <is>
+          <t>未命名队列（New York, USA）</t>
+        </is>
+      </c>
+      <c r="V15" s="16" t="inlineStr">
+        <is>
+          <t>显著正相关</t>
+        </is>
+      </c>
+      <c r="W15" s="16" t="inlineStr">
+        <is>
+          <t>母亲教育显著预测婴儿theta EEG功率（F(9,79)=4.22, p&lt;.001），且与词汇量显著相关（r=0.48, p&lt;.001）</t>
+        </is>
+      </c>
+      <c r="X15" s="16" t="inlineStr">
+        <is>
+          <t>F(9,79)=4.22, p&lt;.001; r(maternal education × vocabulary)=0.48, p&lt;.001</t>
+        </is>
+      </c>
+      <c r="Y15" s="16" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Z15" s="16" t="inlineStr">
+        <is>
+          <t>多元线性回归</t>
+        </is>
+      </c>
+      <c r="AA15" s="16" t="inlineStr">
+        <is>
+          <t>儿童年龄、家庭环境（CHAOS）、家庭收入</t>
+        </is>
+      </c>
+      <c r="AB15" s="16" t="inlineStr">
+        <is>
+          <t>未检验正式中介</t>
+        </is>
+      </c>
+      <c r="AC15" s="16" t="inlineStr">
+        <is>
+          <t>语言输入</t>
+        </is>
+      </c>
+      <c r="AD15" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AE15" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AF15" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG15" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH15" s="16" t="n">
+        <v>2</v>
+      </c>
       <c r="AI15" s="17">
         <f>IFERROR(AF15+AG15+AH15,"")</f>
         <v/>
       </c>
-      <c r="AJ15" s="16" t="n"/>
-      <c r="AK15" s="16" t="n"/>
+      <c r="AJ15" s="16" t="inlineStr">
+        <is>
+          <t>rsEEG与词汇量双重分析；母亲教育、词汇量、家庭环境共同进入回归；theta功率反映成熟度</t>
+        </is>
+      </c>
+      <c r="AK15" s="16" t="inlineStr">
+        <is>
+          <t>oo</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="16" t="n"/>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="16" t="n"/>
-      <c r="G16" s="16" t="n"/>
-      <c r="H16" s="16" t="n"/>
-      <c r="I16" s="16" t="n"/>
-      <c r="J16" s="16" t="n"/>
-      <c r="K16" s="16" t="n"/>
-      <c r="L16" s="16" t="n"/>
-      <c r="M16" s="16" t="n"/>
-      <c r="N16" s="16" t="n"/>
-      <c r="O16" s="16" t="n"/>
-      <c r="P16" s="16" t="n"/>
-      <c r="Q16" s="16" t="n"/>
-      <c r="R16" s="16" t="n"/>
-      <c r="S16" s="16" t="n"/>
-      <c r="T16" s="16" t="n"/>
-      <c r="U16" s="16" t="n"/>
-      <c r="V16" s="16" t="n"/>
-      <c r="W16" s="16" t="n"/>
-      <c r="X16" s="16" t="n"/>
-      <c r="Y16" s="16" t="n"/>
-      <c r="Z16" s="16" t="n"/>
-      <c r="AA16" s="16" t="n"/>
-      <c r="AB16" s="16" t="n"/>
-      <c r="AC16" s="16" t="n"/>
-      <c r="AD16" s="16" t="n"/>
-      <c r="AE16" s="16" t="n"/>
-      <c r="AF16" s="16" t="n"/>
-      <c r="AG16" s="16" t="n"/>
-      <c r="AH16" s="16" t="n"/>
+      <c r="A16" s="16" t="n">
+        <v>75</v>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Shephard</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>横断</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>6–12 months</t>
+        </is>
+      </c>
+      <c r="H16" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>infant(1-12m)</t>
+        </is>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>母亲受教育水平（连续变量）</t>
+        </is>
+      </c>
+      <c r="K16" s="16" t="inlineStr">
+        <is>
+          <t>单独报告</t>
+        </is>
+      </c>
+      <c r="L16" s="16" t="inlineStr">
+        <is>
+          <t>连续变量</t>
+        </is>
+      </c>
+      <c r="M16" s="16" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="N16" s="16" t="inlineStr">
+        <is>
+          <t>无其他SES单独报告</t>
+        </is>
+      </c>
+      <c r="O16" s="16" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="P16" s="16" t="inlineStr">
+        <is>
+          <t>静息态脑网络连接强度（rs-fMRI ICA网络）</t>
+        </is>
+      </c>
+      <c r="Q16" s="16" t="inlineStr">
+        <is>
+          <t>静息态</t>
+        </is>
+      </c>
+      <c r="R16" s="16" t="inlineStr">
+        <is>
+          <t>ICA+回归分析</t>
+        </is>
+      </c>
+      <c r="S16" s="16" t="inlineStr">
+        <is>
+          <t>默认模式网络、感觉运动网络等</t>
+        </is>
+      </c>
+      <c r="T16" s="16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U16" s="16" t="inlineStr">
+        <is>
+          <t>未命名队列（UK）</t>
+        </is>
+      </c>
+      <c r="V16" s="16" t="inlineStr">
+        <is>
+          <t>显著负相关</t>
+        </is>
+      </c>
+      <c r="W16" s="16" t="inlineStr">
+        <is>
+          <t>低母亲教育与更弱的默认模式网络连接显著相关（p=0.01），该关联在控制母亲/婴儿年龄和SES后仍显著（p&lt;.02）</t>
+        </is>
+      </c>
+      <c r="X16" s="16" t="inlineStr">
+        <is>
+          <t>p=0.01（网络连接×母亲教育）；控制SES后p&lt;.02</t>
+        </is>
+      </c>
+      <c r="Y16" s="16" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="Z16" s="16" t="inlineStr">
+        <is>
+          <t>ICA回归分析</t>
+        </is>
+      </c>
+      <c r="AA16" s="16" t="inlineStr">
+        <is>
+          <t>母亲年龄、婴儿年龄、总体SES</t>
+        </is>
+      </c>
+      <c r="AB16" s="16" t="inlineStr">
+        <is>
+          <t>未检验中介</t>
+        </is>
+      </c>
+      <c r="AC16" s="16" t="inlineStr">
+        <is>
+          <t>慢性应激</t>
+        </is>
+      </c>
+      <c r="AD16" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AE16" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AF16" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG16" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH16" s="16" t="n">
+        <v>2</v>
+      </c>
       <c r="AI16" s="17">
         <f>IFERROR(AF16+AG16+AH16,"")</f>
         <v/>
       </c>
-      <c r="AJ16" s="16" t="n"/>
-      <c r="AK16" s="16" t="n"/>
+      <c r="AJ16" s="16" t="inlineStr">
+        <is>
+          <t>以低教育关联更弱连接报告（负向关联）；SES控制后效应保持；母亲焦虑和教育水平共同分析</t>
+        </is>
+      </c>
+      <c r="AK16" s="16" t="inlineStr">
+        <is>
+          <t>oo</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="16" t="n"/>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
-      <c r="G17" s="16" t="n"/>
-      <c r="H17" s="16" t="n"/>
-      <c r="I17" s="16" t="n"/>
-      <c r="J17" s="16" t="n"/>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="16" t="n"/>
-      <c r="M17" s="16" t="n"/>
-      <c r="N17" s="16" t="n"/>
-      <c r="O17" s="16" t="n"/>
-      <c r="P17" s="16" t="n"/>
-      <c r="Q17" s="16" t="n"/>
-      <c r="R17" s="16" t="n"/>
-      <c r="S17" s="16" t="n"/>
-      <c r="T17" s="16" t="n"/>
-      <c r="U17" s="16" t="n"/>
-      <c r="V17" s="16" t="n"/>
-      <c r="W17" s="16" t="n"/>
-      <c r="X17" s="16" t="n"/>
-      <c r="Y17" s="16" t="n"/>
-      <c r="Z17" s="16" t="n"/>
-      <c r="AA17" s="16" t="n"/>
-      <c r="AB17" s="16" t="n"/>
-      <c r="AC17" s="16" t="n"/>
-      <c r="AD17" s="16" t="n"/>
-      <c r="AE17" s="16" t="n"/>
-      <c r="AF17" s="16" t="n"/>
-      <c r="AG17" s="16" t="n"/>
-      <c r="AH17" s="16" t="n"/>
+      <c r="A17" s="16" t="n">
+        <v>78</v>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Conejero</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>2018</v>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>横断</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>56</v>
+      </c>
+      <c r="G17" s="16" t="inlineStr">
+        <is>
+          <t>12–30 months（toddler）</t>
+        </is>
+      </c>
+      <c r="H17" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>toddler(1-3y)</t>
+        </is>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>父母教育水平（连续变量）</t>
+        </is>
+      </c>
+      <c r="K17" s="16" t="inlineStr">
+        <is>
+          <t>单独报告</t>
+        </is>
+      </c>
+      <c r="L17" s="16" t="inlineStr">
+        <is>
+          <t>连续变量</t>
+        </is>
+      </c>
+      <c r="M17" s="16" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="N17" s="16" t="inlineStr">
+        <is>
+          <t>家庭收入</t>
+        </is>
+      </c>
+      <c r="O17" s="16" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+      <c r="P17" s="16" t="inlineStr">
+        <is>
+          <t>ERN振幅+错误后theta功率</t>
+        </is>
+      </c>
+      <c r="Q17" s="16" t="inlineStr">
+        <is>
+          <t>任务态-go-nogo</t>
+        </is>
+      </c>
+      <c r="R17" s="16" t="inlineStr">
+        <is>
+          <t>简单线性回归</t>
+        </is>
+      </c>
+      <c r="S17" s="16" t="inlineStr">
+        <is>
+          <t>前额区（Fz, FCz）</t>
+        </is>
+      </c>
+      <c r="T17" s="16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U17" s="16" t="inlineStr">
+        <is>
+          <t>未命名队列（Granada, Spain）</t>
+        </is>
+      </c>
+      <c r="V17" s="16" t="inlineStr">
+        <is>
+          <t>显著正相关</t>
+        </is>
+      </c>
+      <c r="W17" s="16" t="inlineStr">
+        <is>
+          <t>父母教育水平显著预测幼儿ERN振幅和错误后theta功率增强（p&lt;.05），教育越高误差监控神经指标越强</t>
+        </is>
+      </c>
+      <c r="X17" s="16" t="inlineStr">
+        <is>
+          <t>parental education significantly predicted ERN amplitude and error-related theta, p&lt;.05</t>
+        </is>
+      </c>
+      <c r="Y17" s="16" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Z17" s="16" t="inlineStr">
+        <is>
+          <t>简单线性回归</t>
+        </is>
+      </c>
+      <c r="AA17" s="16" t="inlineStr">
+        <is>
+          <t>儿童年龄、性别</t>
+        </is>
+      </c>
+      <c r="AB17" s="16" t="inlineStr">
+        <is>
+          <t>未检验中介</t>
+        </is>
+      </c>
+      <c r="AC17" s="16" t="inlineStr">
+        <is>
+          <t>认知刺激</t>
+        </is>
+      </c>
+      <c r="AD17" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AE17" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AF17" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG17" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH17" s="16" t="n">
+        <v>2</v>
+      </c>
       <c r="AI17" s="17">
         <f>IFERROR(AF17+AG17+AH17,"")</f>
         <v/>
       </c>
-      <c r="AJ17" s="16" t="n"/>
-      <c r="AK17" s="16" t="n"/>
+      <c r="AJ17" s="16" t="inlineStr">
+        <is>
+          <t>错误监控（ERN）研究；幼儿样本；父母教育作为单一预测变量进入回归；家庭SES（含收入）同时分析</t>
+        </is>
+      </c>
+      <c r="AK17" s="16" t="inlineStr">
+        <is>
+          <t>oo</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="16" t="n"/>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="16" t="n"/>
-      <c r="H18" s="16" t="n"/>
-      <c r="I18" s="16" t="n"/>
-      <c r="J18" s="16" t="n"/>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="16" t="n"/>
-      <c r="M18" s="16" t="n"/>
-      <c r="N18" s="16" t="n"/>
-      <c r="O18" s="16" t="n"/>
-      <c r="P18" s="16" t="n"/>
-      <c r="Q18" s="16" t="n"/>
-      <c r="R18" s="16" t="n"/>
-      <c r="S18" s="16" t="n"/>
-      <c r="T18" s="16" t="n"/>
-      <c r="U18" s="16" t="n"/>
-      <c r="V18" s="16" t="n"/>
-      <c r="W18" s="16" t="n"/>
-      <c r="X18" s="16" t="n"/>
-      <c r="Y18" s="16" t="n"/>
-      <c r="Z18" s="16" t="n"/>
-      <c r="AA18" s="16" t="n"/>
-      <c r="AB18" s="16" t="n"/>
-      <c r="AC18" s="16" t="n"/>
-      <c r="AD18" s="16" t="n"/>
-      <c r="AE18" s="16" t="n"/>
-      <c r="AF18" s="16" t="n"/>
-      <c r="AG18" s="16" t="n"/>
-      <c r="AH18" s="16" t="n"/>
+      <c r="A18" s="16" t="n">
+        <v>79</v>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>Ding</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>横断</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="n">
+        <v>86</v>
+      </c>
+      <c r="G18" s="16" t="inlineStr">
+        <is>
+          <t>12–24 months（toddler）</t>
+        </is>
+      </c>
+      <c r="H18" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>toddler(1-3y)</t>
+        </is>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>父母教育水平（连续变量）</t>
+        </is>
+      </c>
+      <c r="K18" s="16" t="inlineStr">
+        <is>
+          <t>单独报告</t>
+        </is>
+      </c>
+      <c r="L18" s="16" t="inlineStr">
+        <is>
+          <t>连续变量</t>
+        </is>
+      </c>
+      <c r="M18" s="16" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="N18" s="16" t="inlineStr">
+        <is>
+          <t>家庭收入、家庭教养环境（HRE）</t>
+        </is>
+      </c>
+      <c r="O18" s="16" t="inlineStr">
+        <is>
+          <t>fNIRS</t>
+        </is>
+      </c>
+      <c r="P18" s="16" t="inlineStr">
+        <is>
+          <t>前额叶激活（oxyHb）</t>
+        </is>
+      </c>
+      <c r="Q18" s="16" t="inlineStr">
+        <is>
+          <t>任务态-social</t>
+        </is>
+      </c>
+      <c r="R18" s="16" t="inlineStr">
+        <is>
+          <t>GLM回归</t>
+        </is>
+      </c>
+      <c r="S18" s="16" t="inlineStr">
+        <is>
+          <t>前额叶（PFC）</t>
+        </is>
+      </c>
+      <c r="T18" s="16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U18" s="16" t="inlineStr">
+        <is>
+          <t>未命名队列（中国）</t>
+        </is>
+      </c>
+      <c r="V18" s="16" t="inlineStr">
+        <is>
+          <t>显著正相关</t>
+        </is>
+      </c>
+      <c r="W18" s="16" t="inlineStr">
+        <is>
+          <t>高父母教育水平与幼儿联合注意任务中更强的前额叶fNIRS激活相关（p&lt;.05）</t>
+        </is>
+      </c>
+      <c r="X18" s="16" t="inlineStr">
+        <is>
+          <t>Higher parental education level associated with prefrontal activation, p&lt;.05</t>
+        </is>
+      </c>
+      <c r="Y18" s="16" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Z18" s="16" t="inlineStr">
+        <is>
+          <t>GLM回归</t>
+        </is>
+      </c>
+      <c r="AA18" s="16" t="inlineStr">
+        <is>
+          <t>儿童年龄、性别、家庭收入、家庭教养环境</t>
+        </is>
+      </c>
+      <c r="AB18" s="16" t="inlineStr">
+        <is>
+          <t>未检验中介</t>
+        </is>
+      </c>
+      <c r="AC18" s="16" t="inlineStr">
+        <is>
+          <t>认知刺激</t>
+        </is>
+      </c>
+      <c r="AD18" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AE18" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AF18" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG18" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH18" s="16" t="n">
+        <v>2</v>
+      </c>
       <c r="AI18" s="17">
         <f>IFERROR(AF18+AG18+AH18,"")</f>
         <v/>
       </c>
-      <c r="AJ18" s="16" t="n"/>
-      <c r="AK18" s="16" t="n"/>
+      <c r="AJ18" s="16" t="inlineStr">
+        <is>
+          <t>fNIRS联合注意任务；中国样本；父母教育与HRE共同进入回归模型</t>
+        </is>
+      </c>
+      <c r="AK18" s="16" t="inlineStr">
+        <is>
+          <t>oo</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="16" t="n"/>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="16" t="n"/>
-      <c r="H19" s="16" t="n"/>
-      <c r="I19" s="16" t="n"/>
-      <c r="J19" s="16" t="n"/>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="16" t="n"/>
-      <c r="M19" s="16" t="n"/>
-      <c r="N19" s="16" t="n"/>
-      <c r="O19" s="16" t="n"/>
-      <c r="P19" s="16" t="n"/>
-      <c r="Q19" s="16" t="n"/>
-      <c r="R19" s="16" t="n"/>
-      <c r="S19" s="16" t="n"/>
-      <c r="T19" s="16" t="n"/>
-      <c r="U19" s="16" t="n"/>
-      <c r="V19" s="16" t="n"/>
-      <c r="W19" s="16" t="n"/>
-      <c r="X19" s="16" t="n"/>
-      <c r="Y19" s="16" t="n"/>
-      <c r="Z19" s="16" t="n"/>
-      <c r="AA19" s="16" t="n"/>
-      <c r="AB19" s="16" t="n"/>
-      <c r="AC19" s="16" t="n"/>
-      <c r="AD19" s="16" t="n"/>
-      <c r="AE19" s="16" t="n"/>
-      <c r="AF19" s="16" t="n"/>
-      <c r="AG19" s="16" t="n"/>
-      <c r="AH19" s="16" t="n"/>
+      <c r="A19" s="16" t="n">
+        <v>104</v>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>Ursache</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>横断</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>107</v>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
+        <is>
+          <t>3–21 years（重点6–9岁）</t>
+        </is>
+      </c>
+      <c r="H19" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>early-school(6-8y)</t>
+        </is>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>父母受教育年数（连续变量）</t>
+        </is>
+      </c>
+      <c r="K19" s="16" t="inlineStr">
+        <is>
+          <t>单独报告</t>
+        </is>
+      </c>
+      <c r="L19" s="16" t="inlineStr">
+        <is>
+          <t>连续变量</t>
+        </is>
+      </c>
+      <c r="M19" s="16" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="N19" s="16" t="inlineStr">
+        <is>
+          <t>家庭收入（income-to-needs）</t>
+        </is>
+      </c>
+      <c r="O19" s="16" t="inlineStr">
+        <is>
+          <t>DTI</t>
+        </is>
+      </c>
+      <c r="P19" s="16" t="inlineStr">
+        <is>
+          <t>白质FA（fractional anisotropy）</t>
+        </is>
+      </c>
+      <c r="Q19" s="16" t="inlineStr">
+        <is>
+          <t>结构</t>
+        </is>
+      </c>
+      <c r="R19" s="16" t="inlineStr">
+        <is>
+          <t>多元线性回归</t>
+        </is>
+      </c>
+      <c r="S19" s="16" t="inlineStr">
+        <is>
+          <t>全脑白质束（corpus callosum等）</t>
+        </is>
+      </c>
+      <c r="T19" s="16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U19" s="16" t="inlineStr">
+        <is>
+          <t>未命名队列（New York, USA）</t>
+        </is>
+      </c>
+      <c r="V19" s="16" t="inlineStr">
+        <is>
+          <t>显著正相关</t>
+        </is>
+      </c>
+      <c r="W19" s="16" t="inlineStr">
+        <is>
+          <t>父母教育水平与更高的白质FA显著正相关，且与更好的执行功能相关（p=.001）</t>
+        </is>
+      </c>
+      <c r="X19" s="16" t="inlineStr">
+        <is>
+          <t>parental education × WM FA: p=.001; parental education × EF scores: p&lt;.05; r(income, education)=.546</t>
+        </is>
+      </c>
+      <c r="Y19" s="16" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Z19" s="16" t="inlineStr">
+        <is>
+          <t>多元线性回归</t>
+        </is>
+      </c>
+      <c r="AA19" s="16" t="inlineStr">
+        <is>
+          <t>儿童年龄、性别、家庭收入</t>
+        </is>
+      </c>
+      <c r="AB19" s="16" t="inlineStr">
+        <is>
+          <t>白质FA中介教育对执行功能的影响（未正式检验）</t>
+        </is>
+      </c>
+      <c r="AC19" s="16" t="inlineStr">
+        <is>
+          <t>认知刺激</t>
+        </is>
+      </c>
+      <c r="AD19" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AE19" s="16" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AF19" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG19" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH19" s="16" t="n">
+        <v>3</v>
+      </c>
       <c r="AI19" s="17">
         <f>IFERROR(AF19+AG19+AH19,"")</f>
         <v/>
       </c>
-      <c r="AJ19" s="16" t="n"/>
-      <c r="AK19" s="16" t="n"/>
+      <c r="AJ19" s="16" t="inlineStr">
+        <is>
+          <t>收入与教育高度相关r=.546；两变量同时进入回归；教育效应在控制收入后仍显著</t>
+        </is>
+      </c>
+      <c r="AK19" s="16" t="inlineStr">
+        <is>
+          <t>oo</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="16" t="n"/>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="16" t="n"/>
-      <c r="H20" s="16" t="n"/>
-      <c r="I20" s="16" t="n"/>
-      <c r="J20" s="16" t="n"/>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="16" t="n"/>
-      <c r="M20" s="16" t="n"/>
-      <c r="N20" s="16" t="n"/>
-      <c r="O20" s="16" t="n"/>
-      <c r="P20" s="16" t="n"/>
-      <c r="Q20" s="16" t="n"/>
-      <c r="R20" s="16" t="n"/>
-      <c r="S20" s="16" t="n"/>
-      <c r="T20" s="16" t="n"/>
-      <c r="U20" s="16" t="n"/>
-      <c r="V20" s="16" t="n"/>
-      <c r="W20" s="16" t="n"/>
-      <c r="X20" s="16" t="n"/>
-      <c r="Y20" s="16" t="n"/>
-      <c r="Z20" s="16" t="n"/>
-      <c r="AA20" s="16" t="n"/>
-      <c r="AB20" s="16" t="n"/>
-      <c r="AC20" s="16" t="n"/>
-      <c r="AD20" s="16" t="n"/>
-      <c r="AE20" s="16" t="n"/>
-      <c r="AF20" s="16" t="n"/>
-      <c r="AG20" s="16" t="n"/>
-      <c r="AH20" s="16" t="n"/>
+      <c r="A20" s="16" t="n">
+        <v>109</v>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Lange</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>横断</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>309</v>
+      </c>
+      <c r="G20" s="16" t="inlineStr">
+        <is>
+          <t>4–18 years</t>
+        </is>
+      </c>
+      <c r="H20" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="16" t="inlineStr">
+        <is>
+          <t>early-school(6-8y)</t>
+        </is>
+      </c>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>父母最高学历（有序多分类：高中至研究生）</t>
+        </is>
+      </c>
+      <c r="K20" s="16" t="inlineStr">
+        <is>
+          <t>单独报告</t>
+        </is>
+      </c>
+      <c r="L20" s="16" t="inlineStr">
+        <is>
+          <t>多分类</t>
+        </is>
+      </c>
+      <c r="M20" s="16" t="inlineStr">
+        <is>
+          <t>group-comparison</t>
+        </is>
+      </c>
+      <c r="N20" s="16" t="inlineStr">
+        <is>
+          <t>家庭调整收入（AFI）</t>
+        </is>
+      </c>
+      <c r="O20" s="16" t="inlineStr">
+        <is>
+          <t>sMRI</t>
+        </is>
+      </c>
+      <c r="P20" s="16" t="inlineStr">
+        <is>
+          <t>IQ（VIQ/PIQ/FSIQ）及脑体积（TBV/lobar GM/WM）</t>
+        </is>
+      </c>
+      <c r="Q20" s="16" t="inlineStr">
+        <is>
+          <t>结构</t>
+        </is>
+      </c>
+      <c r="R20" s="16" t="inlineStr">
+        <is>
+          <t>多元线性回归（AIC模型选择）</t>
+        </is>
+      </c>
+      <c r="S20" s="16" t="inlineStr">
+        <is>
+          <t>全脑及额颞顶枕叶</t>
+        </is>
+      </c>
+      <c r="T20" s="16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U20" s="16" t="inlineStr">
+        <is>
+          <t>MRI normative sample（UK）</t>
+        </is>
+      </c>
+      <c r="V20" s="16" t="inlineStr">
+        <is>
+          <t>显著正相关</t>
+        </is>
+      </c>
+      <c r="W20" s="16" t="inlineStr">
+        <is>
+          <t>父母教育水平与VIQ显著正相关，父母大学毕业比高中毕业VIQ高14–15分（p&lt;.00001）；PIQ增加8–10分（p=.004）</t>
+        </is>
+      </c>
+      <c r="X20" s="16" t="inlineStr">
+        <is>
+          <t>VIQ: +14–15 pts if parents college grad, p&lt;.00001; PIQ: +8–10 pts, p=.004; FSIQ p&lt;.05</t>
+        </is>
+      </c>
+      <c r="Y20" s="16" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="Z20" s="16" t="inlineStr">
+        <is>
+          <t>多元线性回归（AIC选择）+分组比较</t>
+        </is>
+      </c>
+      <c r="AA20" s="16" t="inlineStr">
+        <is>
+          <t>儿童年龄、性别、家庭调整收入</t>
+        </is>
+      </c>
+      <c r="AB20" s="16" t="inlineStr">
+        <is>
+          <t>父母教育对IQ的影响不经由脑体积中介</t>
+        </is>
+      </c>
+      <c r="AC20" s="16" t="inlineStr">
+        <is>
+          <t>认知刺激</t>
+        </is>
+      </c>
+      <c r="AD20" s="16" t="inlineStr">
+        <is>
+          <t>中介分析</t>
+        </is>
+      </c>
+      <c r="AE20" s="16" t="inlineStr">
+        <is>
+          <t>不显著（教育→IQ不通过脑体积）</t>
+        </is>
+      </c>
+      <c r="AF20" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG20" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH20" s="16" t="n">
+        <v>2</v>
+      </c>
       <c r="AI20" s="17">
         <f>IFERROR(AF20+AG20+AH20,"")</f>
         <v/>
       </c>
-      <c r="AJ20" s="16" t="n"/>
-      <c r="AK20" s="16" t="n"/>
+      <c r="AJ20" s="16" t="inlineStr">
+        <is>
+          <t>结局变量是IQ而非直接脑结构；脑体积是协变量；年龄跨度大（4-18岁）；收入与教育分开报告均有独立效应</t>
+        </is>
+      </c>
+      <c r="AK20" s="16" t="inlineStr">
+        <is>
+          <t>oo</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="16" t="n"/>

--- a/projects/paper-02/04-extract/数据_7_数据提取表_v1.xlsx
+++ b/projects/paper-02/04-extract/数据_7_数据提取表_v1.xlsx
@@ -2747,7 +2747,7 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>Troller-Renfree</t>
+          <t>Turesky</t>
         </is>
       </c>
       <c r="C14" s="16" t="n">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
-          <t>纵向</t>
+          <t>横断</t>
         </is>
       </c>
       <c r="F14" s="16" t="n">
@@ -2768,11 +2768,11 @@
       </c>
       <c r="G14" s="16" t="inlineStr">
         <is>
-          <t>出生→2岁（birth→8.6 months扫描）</t>
+          <t>infants (mean age 8.6 months)</t>
         </is>
       </c>
       <c r="H14" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" s="16" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="N14" s="16" t="inlineStr">
         <is>
-          <t>无其他SES指标单独报告</t>
+          <t>家庭SES（综合）</t>
         </is>
       </c>
       <c r="O14" s="16" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="P14" s="16" t="inlineStr">
         <is>
-          <t>白质FA（fractional anisotropy）</t>
+          <t>白质FA（left SLF等）</t>
         </is>
       </c>
       <c r="Q14" s="16" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="S14" s="16" t="inlineStr">
         <is>
-          <t>全脑白质束</t>
+          <t>左侧SLF、弓状束等</t>
         </is>
       </c>
       <c r="T14" s="16" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="U14" s="16" t="inlineStr">
         <is>
-          <t>未命名队列（Baby Connectome Project子集）</t>
+          <t>Baby Connectome Project子集（USA）</t>
         </is>
       </c>
       <c r="V14" s="16" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="W14" s="16" t="inlineStr">
         <is>
-          <t>母亲教育年数与婴儿期白质FA显著正相关（r=0.48, p&lt;.05），且家庭读写环境（StimQ-Reading）中介该关联</t>
+          <t>母亲教育年数与婴儿期左侧SLF白质FA显著正相关（FWE校正后显著）；家庭读写环境（StimQ-Reading）中介该关联</t>
         </is>
       </c>
       <c r="X14" s="16" t="inlineStr">
         <is>
-          <t>r=0.48, p&lt;.05</t>
+          <t>r=0.48, p&lt;.05; maternal education × left SLF FA significant after FWE correction</t>
         </is>
       </c>
       <c r="Y14" s="16" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="AJ14" s="16" t="inlineStr">
         <is>
-          <t>N=38，样本量较小；家庭读写环境（StimQ-Reading）作为中介变量；双语/多文化样本</t>
+          <t>N=38，样本量小；第一作者为Turesky（非Troller-Renfree）；家庭读写环境作为中介变量</t>
         </is>
       </c>
       <c r="AK14" s="16" t="inlineStr">
         <is>
-          <t>oo</t>
+          <t>oo修正</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>Tomalski</t>
+          <t>Maguire</t>
         </is>
       </c>
       <c r="C15" s="16" t="n">
@@ -2936,11 +2936,11 @@
         </is>
       </c>
       <c r="F15" s="16" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G15" s="16" t="inlineStr">
         <is>
-          <t>6–24 months</t>
+          <t>grade school (6-12 years)</t>
         </is>
       </c>
       <c r="H15" s="16" t="n">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="I15" s="16" t="inlineStr">
         <is>
-          <t>infant(1-12m)</t>
+          <t>school-age(6-13y)</t>
         </is>
       </c>
       <c r="J15" s="16" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="M15" s="16" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="N15" s="16" t="inlineStr">
         <is>
-          <t>家庭词汇环境、CHAOS量表</t>
+          <t>家庭收入（free/reduced lunch资格）</t>
         </is>
       </c>
       <c r="O15" s="16" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="P15" s="16" t="inlineStr">
         <is>
-          <t>静息态EEG功率（theta频段）</t>
+          <t>静息态EEG功率（alpha/theta频段）</t>
         </is>
       </c>
       <c r="Q15" s="16" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="R15" s="16" t="inlineStr">
         <is>
-          <t>多元线性回归</t>
+          <t>层级多元线性回归</t>
         </is>
       </c>
       <c r="S15" s="16" t="inlineStr">
         <is>
-          <t>全脑（Fz, Cz, Pz等）</t>
+          <t>左额中央区（alpha）、右顶区（theta）</t>
         </is>
       </c>
       <c r="T15" s="16" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="U15" s="16" t="inlineStr">
         <is>
-          <t>未命名队列（New York, USA）</t>
+          <t>未命名队列（Texas &amp; Delaware, USA）</t>
         </is>
       </c>
       <c r="V15" s="16" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="W15" s="16" t="inlineStr">
         <is>
-          <t>母亲教育显著预测婴儿theta EEG功率（F(9,79)=4.22, p&lt;.001），且与词汇量显著相关（r=0.48, p&lt;.001）</t>
+          <t>母亲教育显著预测词汇量（β=0.31, t=2.24, p=.02），独立于收入；低收入儿童alpha功率更低（t(44)=2.45, p=.02），theta功率更高（t(44)=-2.80, p=.007）</t>
         </is>
       </c>
       <c r="X15" s="16" t="inlineStr">
         <is>
-          <t>F(9,79)=4.22, p&lt;.001; r(maternal education × vocabulary)=0.48, p&lt;.001</t>
+          <t>β=0.31, t=2.24, p=.02 (vocabulary); alpha: t(44)=2.45, p=.02; theta: t(44)=-2.80, p=.007</t>
         </is>
       </c>
       <c r="Y15" s="16" t="inlineStr">
@@ -3033,17 +3033,17 @@
       </c>
       <c r="Z15" s="16" t="inlineStr">
         <is>
-          <t>多元线性回归</t>
+          <t>层级多元线性回归（控制年龄、民族、双语、收入、CHAOS）</t>
         </is>
       </c>
       <c r="AA15" s="16" t="inlineStr">
         <is>
-          <t>儿童年龄、家庭环境（CHAOS）、家庭收入</t>
+          <t>儿童年龄、民族、双语状态、家庭收入、家庭环境（CHAOS）</t>
         </is>
       </c>
       <c r="AB15" s="16" t="inlineStr">
         <is>
-          <t>未检验正式中介</t>
+          <t>EEG alpha/theta功率中介收入→认知关联（非正式检验）</t>
         </is>
       </c>
       <c r="AC15" s="16" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="AJ15" s="16" t="inlineStr">
         <is>
-          <t>rsEEG与词汇量双重分析；母亲教育、词汇量、家庭环境共同进入回归；theta功率反映成熟度</t>
+          <t>主暴露为家庭收入（分组），母亲教育作为连续变量独立进入回归；双语儿童占比高；结局为词汇量和工作记忆（非直接脑指标）</t>
         </is>
       </c>
       <c r="AK15" s="16" t="inlineStr">
         <is>
-          <t>oo</t>
+          <t>oo修正</t>
         </is>
       </c>
     </row>

--- a/projects/paper-02/04-extract/数据_7_数据提取表_v1.xlsx
+++ b/projects/paper-02/04-extract/数据_7_数据提取表_v1.xlsx
@@ -3200,12 +3200,12 @@
       </c>
       <c r="Y16" s="16" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="Z16" s="16" t="inlineStr">
         <is>
-          <t>ICA回归分析</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="AA16" s="16" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="AJ16" s="16" t="inlineStr">
         <is>
-          <t>以低教育关联更弱连接报告（负向关联）；SES控制后效应保持；母亲焦虑和教育水平共同分析</t>
+          <t>以低教育关联更弱连接报告（负向关联）；SES控制后效应保持；母亲焦虑和教育水平共同分析；D3b编码修正：低教育→弱连接=教育正向预测连接强度，改positive</t>
         </is>
       </c>
       <c r="AK16" s="16" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="I19" s="16" t="inlineStr">
         <is>
-          <t>early-school(6-8y)</t>
+          <t>mixed(3-21y)</t>
         </is>
       </c>
       <c r="J19" s="16" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
-          <t>early-school(6-8y)</t>
+          <t>mixed(4-18y)</t>
         </is>
       </c>
       <c r="J20" s="16" t="inlineStr">

--- a/projects/paper-02/04-extract/数据_7_数据提取表_v1.xlsx
+++ b/projects/paper-02/04-extract/数据_7_数据提取表_v1.xlsx
@@ -2940,7 +2940,7 @@
       </c>
       <c r="G15" s="16" t="inlineStr">
         <is>
-          <t>grade school (6-12 years)</t>
+          <t>8–15 years (grade school)</t>
         </is>
       </c>
       <c r="H15" s="16" t="n">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="AJ15" s="16" t="inlineStr">
         <is>
-          <t>主暴露为家庭收入（分组），母亲教育作为连续变量独立进入回归；双语儿童占比高；结局为词汇量和工作记忆（非直接脑指标）</t>
+          <t>主暴露为家庭收入（分组），母亲教育作为连续变量独立进入回归；双语儿童占比高；结局为词汇量和工作记忆（非直接脑指标）；年龄范围8–15岁</t>
         </is>
       </c>
       <c r="AK15" s="16" t="inlineStr">
         <is>
-          <t>oo修正</t>
+          <t>oo修正(年龄)</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="X17" s="16" t="inlineStr">
         <is>
-          <t>parental education significantly predicted ERN amplitude and error-related theta, p&lt;.05</t>
+          <t>ERN: β=.355, F(1,51)=7.10, p&lt;.05; error-related theta: β=.25, F(1,51)=3.47, p&lt;.07</t>
         </is>
       </c>
       <c r="Y17" s="16" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="AJ17" s="16" t="inlineStr">
         <is>
-          <t>错误监控（ERN）研究；幼儿样本；父母教育作为单一预测变量进入回归；家庭SES（含收入）同时分析</t>
+          <t>错误监控（ERN）研究；幼儿样本；ERN β=.355 p&lt;.05（显著），theta β=.25 p&lt;.07（边界显著）；父母教育作为单一预测变量进入简单线性回归</t>
         </is>
       </c>
       <c r="AK17" s="16" t="inlineStr">
         <is>
-          <t>oo</t>
+          <t>oo补充β值</t>
         </is>
       </c>
     </row>

--- a/projects/paper-02/04-extract/数据_7_数据提取表_v1.xlsx
+++ b/projects/paper-02/04-extract/数据_7_数据提取表_v1.xlsx
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK203"/>
+  <dimension ref="A1:AK202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3431,19 +3431,19 @@
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="16" t="n">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>Ding</t>
+          <t>Ursache</t>
         </is>
       </c>
       <c r="C18" s="16" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E18" s="16" t="inlineStr">
@@ -3452,11 +3452,11 @@
         </is>
       </c>
       <c r="F18" s="16" t="n">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="G18" s="16" t="inlineStr">
         <is>
-          <t>12–24 months（toddler）</t>
+          <t>3–21 years（重点6–9岁）</t>
         </is>
       </c>
       <c r="H18" s="16" t="n">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="I18" s="16" t="inlineStr">
         <is>
-          <t>toddler(1-3y)</t>
+          <t>mixed(3-21y)</t>
         </is>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>父母教育水平（连续变量）</t>
+          <t>父母受教育年数（连续变量）</t>
         </is>
       </c>
       <c r="K18" s="16" t="inlineStr">
@@ -3484,37 +3484,37 @@
       </c>
       <c r="M18" s="16" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>r</t>
         </is>
       </c>
       <c r="N18" s="16" t="inlineStr">
         <is>
-          <t>家庭收入、家庭教养环境（HRE）</t>
+          <t>家庭收入（income-to-needs）</t>
         </is>
       </c>
       <c r="O18" s="16" t="inlineStr">
         <is>
-          <t>fNIRS</t>
+          <t>DTI</t>
         </is>
       </c>
       <c r="P18" s="16" t="inlineStr">
         <is>
-          <t>前额叶激活（oxyHb）</t>
+          <t>白质FA（fractional anisotropy）</t>
         </is>
       </c>
       <c r="Q18" s="16" t="inlineStr">
         <is>
-          <t>任务态-social</t>
+          <t>结构</t>
         </is>
       </c>
       <c r="R18" s="16" t="inlineStr">
         <is>
-          <t>GLM回归</t>
+          <t>多元线性回归</t>
         </is>
       </c>
       <c r="S18" s="16" t="inlineStr">
         <is>
-          <t>前额叶（PFC）</t>
+          <t>全脑白质束（corpus callosum等）</t>
         </is>
       </c>
       <c r="T18" s="16" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="U18" s="16" t="inlineStr">
         <is>
-          <t>未命名队列（中国）</t>
+          <t>未命名队列（New York, USA）</t>
         </is>
       </c>
       <c r="V18" s="16" t="inlineStr">
@@ -3534,12 +3534,12 @@
       </c>
       <c r="W18" s="16" t="inlineStr">
         <is>
-          <t>高父母教育水平与幼儿联合注意任务中更强的前额叶fNIRS激活相关（p&lt;.05）</t>
+          <t>父母教育水平与更高的白质FA显著正相关，且与更好的执行功能相关（p=.001）</t>
         </is>
       </c>
       <c r="X18" s="16" t="inlineStr">
         <is>
-          <t>Higher parental education level associated with prefrontal activation, p&lt;.05</t>
+          <t>parental education × WM FA: p=.001; parental education × EF scores: p&lt;.05; r(income, education)=.546</t>
         </is>
       </c>
       <c r="Y18" s="16" t="inlineStr">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="Z18" s="16" t="inlineStr">
         <is>
-          <t>GLM回归</t>
+          <t>多元线性回归</t>
         </is>
       </c>
       <c r="AA18" s="16" t="inlineStr">
         <is>
-          <t>儿童年龄、性别、家庭收入、家庭教养环境</t>
+          <t>儿童年龄、性别、家庭收入</t>
         </is>
       </c>
       <c r="AB18" s="16" t="inlineStr">
         <is>
-          <t>未检验中介</t>
+          <t>白质FA中介教育对执行功能的影响（未正式检验）</t>
         </is>
       </c>
       <c r="AC18" s="16" t="inlineStr">
@@ -3584,15 +3584,15 @@
         <v>2</v>
       </c>
       <c r="AH18" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI18" s="17">
-        <f>IFERROR(AF18+AG18+AH18,"")</f>
+        <f>IFERROR(AF19+AG19+AH19,"")</f>
         <v/>
       </c>
       <c r="AJ18" s="16" t="inlineStr">
         <is>
-          <t>fNIRS联合注意任务；中国样本；父母教育与HRE共同进入回归模型</t>
+          <t>收入与教育高度相关r=.546；两变量同时进入回归；教育效应在控制收入后仍显著</t>
         </is>
       </c>
       <c r="AK18" s="16" t="inlineStr">
@@ -3603,19 +3603,19 @@
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="16" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>Ursache</t>
+          <t>Lange</t>
         </is>
       </c>
       <c r="C19" s="16" t="n">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E19" s="16" t="inlineStr">
@@ -3624,11 +3624,11 @@
         </is>
       </c>
       <c r="F19" s="16" t="n">
-        <v>107</v>
+        <v>309</v>
       </c>
       <c r="G19" s="16" t="inlineStr">
         <is>
-          <t>3–21 years（重点6–9岁）</t>
+          <t>4–18 years</t>
         </is>
       </c>
       <c r="H19" s="16" t="n">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="I19" s="16" t="inlineStr">
         <is>
-          <t>mixed(3-21y)</t>
+          <t>mixed(4-18y)</t>
         </is>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>父母受教育年数（连续变量）</t>
+          <t>父母最高学历（有序多分类：高中至研究生）</t>
         </is>
       </c>
       <c r="K19" s="16" t="inlineStr">
@@ -3651,27 +3651,27 @@
       </c>
       <c r="L19" s="16" t="inlineStr">
         <is>
-          <t>连续变量</t>
+          <t>多分类</t>
         </is>
       </c>
       <c r="M19" s="16" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>group-comparison</t>
         </is>
       </c>
       <c r="N19" s="16" t="inlineStr">
         <is>
-          <t>家庭收入（income-to-needs）</t>
+          <t>家庭调整收入（AFI）</t>
         </is>
       </c>
       <c r="O19" s="16" t="inlineStr">
         <is>
-          <t>DTI</t>
+          <t>sMRI</t>
         </is>
       </c>
       <c r="P19" s="16" t="inlineStr">
         <is>
-          <t>白质FA（fractional anisotropy）</t>
+          <t>IQ（VIQ/PIQ/FSIQ）及脑体积（TBV/lobar GM/WM）</t>
         </is>
       </c>
       <c r="Q19" s="16" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="R19" s="16" t="inlineStr">
         <is>
-          <t>多元线性回归</t>
+          <t>多元线性回归（AIC模型选择）</t>
         </is>
       </c>
       <c r="S19" s="16" t="inlineStr">
         <is>
-          <t>全脑白质束（corpus callosum等）</t>
+          <t>全脑及额颞顶枕叶</t>
         </is>
       </c>
       <c r="T19" s="16" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="U19" s="16" t="inlineStr">
         <is>
-          <t>未命名队列（New York, USA）</t>
+          <t>MRI normative sample（UK）</t>
         </is>
       </c>
       <c r="V19" s="16" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="W19" s="16" t="inlineStr">
         <is>
-          <t>父母教育水平与更高的白质FA显著正相关，且与更好的执行功能相关（p=.001）</t>
+          <t>父母教育水平与VIQ显著正相关，父母大学毕业比高中毕业VIQ高14–15分（p&lt;.00001）；PIQ增加8–10分（p=.004）</t>
         </is>
       </c>
       <c r="X19" s="16" t="inlineStr">
         <is>
-          <t>parental education × WM FA: p=.001; parental education × EF scores: p&lt;.05; r(income, education)=.546</t>
+          <t>VIQ: +14–15 pts if parents college grad, p&lt;.00001; PIQ: +8–10 pts, p=.004; FSIQ p&lt;.05</t>
         </is>
       </c>
       <c r="Y19" s="16" t="inlineStr">
@@ -3721,17 +3721,17 @@
       </c>
       <c r="Z19" s="16" t="inlineStr">
         <is>
-          <t>多元线性回归</t>
+          <t>多元线性回归（AIC选择）+分组比较</t>
         </is>
       </c>
       <c r="AA19" s="16" t="inlineStr">
         <is>
-          <t>儿童年龄、性别、家庭收入</t>
+          <t>儿童年龄、性别、家庭调整收入</t>
         </is>
       </c>
       <c r="AB19" s="16" t="inlineStr">
         <is>
-          <t>白质FA中介教育对执行功能的影响（未正式检验）</t>
+          <t>父母教育对IQ的影响不经由脑体积中介</t>
         </is>
       </c>
       <c r="AC19" s="16" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="AD19" s="16" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>中介分析</t>
         </is>
       </c>
       <c r="AE19" s="16" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>不显著（教育→IQ不通过脑体积）</t>
         </is>
       </c>
       <c r="AF19" s="16" t="n">
@@ -3756,15 +3756,15 @@
         <v>2</v>
       </c>
       <c r="AH19" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI19" s="17">
-        <f>IFERROR(AF19+AG19+AH19,"")</f>
+        <f>IFERROR(AF20+AG20+AH20,"")</f>
         <v/>
       </c>
       <c r="AJ19" s="16" t="inlineStr">
         <is>
-          <t>收入与教育高度相关r=.546；两变量同时进入回归；教育效应在控制收入后仍显著</t>
+          <t>结局变量是IQ而非直接脑结构；脑体积是协变量；年龄跨度大（4-18岁）；收入与教育分开报告均有独立效应</t>
         </is>
       </c>
       <c r="AK19" s="16" t="inlineStr">
@@ -3774,176 +3774,46 @@
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="16" t="n">
-        <v>109</v>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>Lange</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="n">
-        <v>2010</v>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>横断</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="n">
-        <v>309</v>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>4–18 years</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>mixed(4-18y)</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>父母最高学历（有序多分类：高中至研究生）</t>
-        </is>
-      </c>
-      <c r="K20" s="16" t="inlineStr">
-        <is>
-          <t>单独报告</t>
-        </is>
-      </c>
-      <c r="L20" s="16" t="inlineStr">
-        <is>
-          <t>多分类</t>
-        </is>
-      </c>
-      <c r="M20" s="16" t="inlineStr">
-        <is>
-          <t>group-comparison</t>
-        </is>
-      </c>
-      <c r="N20" s="16" t="inlineStr">
-        <is>
-          <t>家庭调整收入（AFI）</t>
-        </is>
-      </c>
-      <c r="O20" s="16" t="inlineStr">
-        <is>
-          <t>sMRI</t>
-        </is>
-      </c>
-      <c r="P20" s="16" t="inlineStr">
-        <is>
-          <t>IQ（VIQ/PIQ/FSIQ）及脑体积（TBV/lobar GM/WM）</t>
-        </is>
-      </c>
-      <c r="Q20" s="16" t="inlineStr">
-        <is>
-          <t>结构</t>
-        </is>
-      </c>
-      <c r="R20" s="16" t="inlineStr">
-        <is>
-          <t>多元线性回归（AIC模型选择）</t>
-        </is>
-      </c>
-      <c r="S20" s="16" t="inlineStr">
-        <is>
-          <t>全脑及额颞顶枕叶</t>
-        </is>
-      </c>
-      <c r="T20" s="16" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="U20" s="16" t="inlineStr">
-        <is>
-          <t>MRI normative sample（UK）</t>
-        </is>
-      </c>
-      <c r="V20" s="16" t="inlineStr">
-        <is>
-          <t>显著正相关</t>
-        </is>
-      </c>
-      <c r="W20" s="16" t="inlineStr">
-        <is>
-          <t>父母教育水平与VIQ显著正相关，父母大学毕业比高中毕业VIQ高14–15分（p&lt;.00001）；PIQ增加8–10分（p=.004）</t>
-        </is>
-      </c>
-      <c r="X20" s="16" t="inlineStr">
-        <is>
-          <t>VIQ: +14–15 pts if parents college grad, p&lt;.00001; PIQ: +8–10 pts, p=.004; FSIQ p&lt;.05</t>
-        </is>
-      </c>
-      <c r="Y20" s="16" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="Z20" s="16" t="inlineStr">
-        <is>
-          <t>多元线性回归（AIC选择）+分组比较</t>
-        </is>
-      </c>
-      <c r="AA20" s="16" t="inlineStr">
-        <is>
-          <t>儿童年龄、性别、家庭调整收入</t>
-        </is>
-      </c>
-      <c r="AB20" s="16" t="inlineStr">
-        <is>
-          <t>父母教育对IQ的影响不经由脑体积中介</t>
-        </is>
-      </c>
-      <c r="AC20" s="16" t="inlineStr">
-        <is>
-          <t>认知刺激</t>
-        </is>
-      </c>
-      <c r="AD20" s="16" t="inlineStr">
-        <is>
-          <t>中介分析</t>
-        </is>
-      </c>
-      <c r="AE20" s="16" t="inlineStr">
-        <is>
-          <t>不显著（教育→IQ不通过脑体积）</t>
-        </is>
-      </c>
-      <c r="AF20" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG20" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH20" s="16" t="n">
-        <v>2</v>
-      </c>
+      <c r="A20" s="16" t="n"/>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="16" t="n"/>
+      <c r="G20" s="16" t="n"/>
+      <c r="H20" s="16" t="n"/>
+      <c r="I20" s="16" t="n"/>
+      <c r="J20" s="16" t="n"/>
+      <c r="K20" s="16" t="n"/>
+      <c r="L20" s="16" t="n"/>
+      <c r="M20" s="16" t="n"/>
+      <c r="N20" s="16" t="n"/>
+      <c r="O20" s="16" t="n"/>
+      <c r="P20" s="16" t="n"/>
+      <c r="Q20" s="16" t="n"/>
+      <c r="R20" s="16" t="n"/>
+      <c r="S20" s="16" t="n"/>
+      <c r="T20" s="16" t="n"/>
+      <c r="U20" s="16" t="n"/>
+      <c r="V20" s="16" t="n"/>
+      <c r="W20" s="16" t="n"/>
+      <c r="X20" s="16" t="n"/>
+      <c r="Y20" s="16" t="n"/>
+      <c r="Z20" s="16" t="n"/>
+      <c r="AA20" s="16" t="n"/>
+      <c r="AB20" s="16" t="n"/>
+      <c r="AC20" s="16" t="n"/>
+      <c r="AD20" s="16" t="n"/>
+      <c r="AE20" s="16" t="n"/>
+      <c r="AF20" s="16" t="n"/>
+      <c r="AG20" s="16" t="n"/>
+      <c r="AH20" s="16" t="n"/>
       <c r="AI20" s="17">
-        <f>IFERROR(AF20+AG20+AH20,"")</f>
-        <v/>
-      </c>
-      <c r="AJ20" s="16" t="inlineStr">
-        <is>
-          <t>结局变量是IQ而非直接脑结构；脑体积是协变量；年龄跨度大（4-18岁）；收入与教育分开报告均有独立效应</t>
-        </is>
-      </c>
-      <c r="AK20" s="16" t="inlineStr">
-        <is>
-          <t>oo</t>
-        </is>
-      </c>
+        <f>IFERROR(AF21+AG21+AH21,"")</f>
+        <v/>
+      </c>
+      <c r="AJ20" s="16" t="n"/>
+      <c r="AK20" s="16" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="16" t="n"/>
@@ -3981,7 +3851,7 @@
       <c r="AG21" s="16" t="n"/>
       <c r="AH21" s="16" t="n"/>
       <c r="AI21" s="17">
-        <f>IFERROR(AF21+AG21+AH21,"")</f>
+        <f>IFERROR(AF22+AG22+AH22,"")</f>
         <v/>
       </c>
       <c r="AJ21" s="16" t="n"/>
@@ -4023,7 +3893,7 @@
       <c r="AG22" s="16" t="n"/>
       <c r="AH22" s="16" t="n"/>
       <c r="AI22" s="17">
-        <f>IFERROR(AF22+AG22+AH22,"")</f>
+        <f>IFERROR(AF23+AG23+AH23,"")</f>
         <v/>
       </c>
       <c r="AJ22" s="16" t="n"/>
@@ -4065,7 +3935,7 @@
       <c r="AG23" s="16" t="n"/>
       <c r="AH23" s="16" t="n"/>
       <c r="AI23" s="17">
-        <f>IFERROR(AF23+AG23+AH23,"")</f>
+        <f>IFERROR(AF24+AG24+AH24,"")</f>
         <v/>
       </c>
       <c r="AJ23" s="16" t="n"/>
@@ -4107,7 +3977,7 @@
       <c r="AG24" s="16" t="n"/>
       <c r="AH24" s="16" t="n"/>
       <c r="AI24" s="17">
-        <f>IFERROR(AF24+AG24+AH24,"")</f>
+        <f>IFERROR(AF25+AG25+AH25,"")</f>
         <v/>
       </c>
       <c r="AJ24" s="16" t="n"/>
@@ -4149,7 +4019,7 @@
       <c r="AG25" s="16" t="n"/>
       <c r="AH25" s="16" t="n"/>
       <c r="AI25" s="17">
-        <f>IFERROR(AF25+AG25+AH25,"")</f>
+        <f>IFERROR(AF26+AG26+AH26,"")</f>
         <v/>
       </c>
       <c r="AJ25" s="16" t="n"/>
@@ -4191,7 +4061,7 @@
       <c r="AG26" s="16" t="n"/>
       <c r="AH26" s="16" t="n"/>
       <c r="AI26" s="17">
-        <f>IFERROR(AF26+AG26+AH26,"")</f>
+        <f>IFERROR(AF27+AG27+AH27,"")</f>
         <v/>
       </c>
       <c r="AJ26" s="16" t="n"/>
@@ -4233,7 +4103,7 @@
       <c r="AG27" s="16" t="n"/>
       <c r="AH27" s="16" t="n"/>
       <c r="AI27" s="17">
-        <f>IFERROR(AF27+AG27+AH27,"")</f>
+        <f>IFERROR(AF28+AG28+AH28,"")</f>
         <v/>
       </c>
       <c r="AJ27" s="16" t="n"/>
@@ -4275,7 +4145,7 @@
       <c r="AG28" s="16" t="n"/>
       <c r="AH28" s="16" t="n"/>
       <c r="AI28" s="17">
-        <f>IFERROR(AF28+AG28+AH28,"")</f>
+        <f>IFERROR(AF29+AG29+AH29,"")</f>
         <v/>
       </c>
       <c r="AJ28" s="16" t="n"/>
@@ -4317,7 +4187,7 @@
       <c r="AG29" s="16" t="n"/>
       <c r="AH29" s="16" t="n"/>
       <c r="AI29" s="17">
-        <f>IFERROR(AF29+AG29+AH29,"")</f>
+        <f>IFERROR(AF30+AG30+AH30,"")</f>
         <v/>
       </c>
       <c r="AJ29" s="16" t="n"/>
@@ -4359,7 +4229,7 @@
       <c r="AG30" s="16" t="n"/>
       <c r="AH30" s="16" t="n"/>
       <c r="AI30" s="17">
-        <f>IFERROR(AF30+AG30+AH30,"")</f>
+        <f>IFERROR(AF31+AG31+AH31,"")</f>
         <v/>
       </c>
       <c r="AJ30" s="16" t="n"/>
@@ -4401,7 +4271,7 @@
       <c r="AG31" s="16" t="n"/>
       <c r="AH31" s="16" t="n"/>
       <c r="AI31" s="17">
-        <f>IFERROR(AF31+AG31+AH31,"")</f>
+        <f>IFERROR(AF32+AG32+AH32,"")</f>
         <v/>
       </c>
       <c r="AJ31" s="16" t="n"/>
@@ -4443,7 +4313,7 @@
       <c r="AG32" s="16" t="n"/>
       <c r="AH32" s="16" t="n"/>
       <c r="AI32" s="17">
-        <f>IFERROR(AF32+AG32+AH32,"")</f>
+        <f>IFERROR(AF33+AG33+AH33,"")</f>
         <v/>
       </c>
       <c r="AJ32" s="16" t="n"/>
@@ -4485,7 +4355,7 @@
       <c r="AG33" s="16" t="n"/>
       <c r="AH33" s="16" t="n"/>
       <c r="AI33" s="17">
-        <f>IFERROR(AF33+AG33+AH33,"")</f>
+        <f>IFERROR(AF34+AG34+AH34,"")</f>
         <v/>
       </c>
       <c r="AJ33" s="16" t="n"/>
@@ -4527,7 +4397,7 @@
       <c r="AG34" s="16" t="n"/>
       <c r="AH34" s="16" t="n"/>
       <c r="AI34" s="17">
-        <f>IFERROR(AF34+AG34+AH34,"")</f>
+        <f>IFERROR(AF35+AG35+AH35,"")</f>
         <v/>
       </c>
       <c r="AJ34" s="16" t="n"/>
@@ -4569,7 +4439,7 @@
       <c r="AG35" s="16" t="n"/>
       <c r="AH35" s="16" t="n"/>
       <c r="AI35" s="17">
-        <f>IFERROR(AF35+AG35+AH35,"")</f>
+        <f>IFERROR(AF36+AG36+AH36,"")</f>
         <v/>
       </c>
       <c r="AJ35" s="16" t="n"/>
@@ -4611,7 +4481,7 @@
       <c r="AG36" s="16" t="n"/>
       <c r="AH36" s="16" t="n"/>
       <c r="AI36" s="17">
-        <f>IFERROR(AF36+AG36+AH36,"")</f>
+        <f>IFERROR(AF37+AG37+AH37,"")</f>
         <v/>
       </c>
       <c r="AJ36" s="16" t="n"/>
@@ -4653,7 +4523,7 @@
       <c r="AG37" s="16" t="n"/>
       <c r="AH37" s="16" t="n"/>
       <c r="AI37" s="17">
-        <f>IFERROR(AF37+AG37+AH37,"")</f>
+        <f>IFERROR(AF38+AG38+AH38,"")</f>
         <v/>
       </c>
       <c r="AJ37" s="16" t="n"/>
@@ -4695,7 +4565,7 @@
       <c r="AG38" s="16" t="n"/>
       <c r="AH38" s="16" t="n"/>
       <c r="AI38" s="17">
-        <f>IFERROR(AF38+AG38+AH38,"")</f>
+        <f>IFERROR(AF39+AG39+AH39,"")</f>
         <v/>
       </c>
       <c r="AJ38" s="16" t="n"/>
@@ -4737,7 +4607,7 @@
       <c r="AG39" s="16" t="n"/>
       <c r="AH39" s="16" t="n"/>
       <c r="AI39" s="17">
-        <f>IFERROR(AF39+AG39+AH39,"")</f>
+        <f>IFERROR(AF40+AG40+AH40,"")</f>
         <v/>
       </c>
       <c r="AJ39" s="16" t="n"/>
@@ -4779,7 +4649,7 @@
       <c r="AG40" s="16" t="n"/>
       <c r="AH40" s="16" t="n"/>
       <c r="AI40" s="17">
-        <f>IFERROR(AF40+AG40+AH40,"")</f>
+        <f>IFERROR(AF41+AG41+AH41,"")</f>
         <v/>
       </c>
       <c r="AJ40" s="16" t="n"/>
@@ -4821,7 +4691,7 @@
       <c r="AG41" s="16" t="n"/>
       <c r="AH41" s="16" t="n"/>
       <c r="AI41" s="17">
-        <f>IFERROR(AF41+AG41+AH41,"")</f>
+        <f>IFERROR(AF42+AG42+AH42,"")</f>
         <v/>
       </c>
       <c r="AJ41" s="16" t="n"/>
@@ -4863,7 +4733,7 @@
       <c r="AG42" s="16" t="n"/>
       <c r="AH42" s="16" t="n"/>
       <c r="AI42" s="17">
-        <f>IFERROR(AF42+AG42+AH42,"")</f>
+        <f>IFERROR(AF43+AG43+AH43,"")</f>
         <v/>
       </c>
       <c r="AJ42" s="16" t="n"/>
@@ -4905,7 +4775,7 @@
       <c r="AG43" s="16" t="n"/>
       <c r="AH43" s="16" t="n"/>
       <c r="AI43" s="17">
-        <f>IFERROR(AF43+AG43+AH43,"")</f>
+        <f>IFERROR(AF44+AG44+AH44,"")</f>
         <v/>
       </c>
       <c r="AJ43" s="16" t="n"/>
@@ -4947,7 +4817,7 @@
       <c r="AG44" s="16" t="n"/>
       <c r="AH44" s="16" t="n"/>
       <c r="AI44" s="17">
-        <f>IFERROR(AF44+AG44+AH44,"")</f>
+        <f>IFERROR(AF45+AG45+AH45,"")</f>
         <v/>
       </c>
       <c r="AJ44" s="16" t="n"/>
@@ -4989,7 +4859,7 @@
       <c r="AG45" s="16" t="n"/>
       <c r="AH45" s="16" t="n"/>
       <c r="AI45" s="17">
-        <f>IFERROR(AF45+AG45+AH45,"")</f>
+        <f>IFERROR(AF46+AG46+AH46,"")</f>
         <v/>
       </c>
       <c r="AJ45" s="16" t="n"/>
@@ -5031,7 +4901,7 @@
       <c r="AG46" s="16" t="n"/>
       <c r="AH46" s="16" t="n"/>
       <c r="AI46" s="17">
-        <f>IFERROR(AF46+AG46+AH46,"")</f>
+        <f>IFERROR(AF47+AG47+AH47,"")</f>
         <v/>
       </c>
       <c r="AJ46" s="16" t="n"/>
@@ -5073,7 +4943,7 @@
       <c r="AG47" s="16" t="n"/>
       <c r="AH47" s="16" t="n"/>
       <c r="AI47" s="17">
-        <f>IFERROR(AF47+AG47+AH47,"")</f>
+        <f>IFERROR(AF48+AG48+AH48,"")</f>
         <v/>
       </c>
       <c r="AJ47" s="16" t="n"/>
@@ -5115,7 +4985,7 @@
       <c r="AG48" s="16" t="n"/>
       <c r="AH48" s="16" t="n"/>
       <c r="AI48" s="17">
-        <f>IFERROR(AF48+AG48+AH48,"")</f>
+        <f>IFERROR(AF49+AG49+AH49,"")</f>
         <v/>
       </c>
       <c r="AJ48" s="16" t="n"/>
@@ -5157,7 +5027,7 @@
       <c r="AG49" s="16" t="n"/>
       <c r="AH49" s="16" t="n"/>
       <c r="AI49" s="17">
-        <f>IFERROR(AF49+AG49+AH49,"")</f>
+        <f>IFERROR(AF50+AG50+AH50,"")</f>
         <v/>
       </c>
       <c r="AJ49" s="16" t="n"/>
@@ -5199,7 +5069,7 @@
       <c r="AG50" s="16" t="n"/>
       <c r="AH50" s="16" t="n"/>
       <c r="AI50" s="17">
-        <f>IFERROR(AF50+AG50+AH50,"")</f>
+        <f>IFERROR(AF51+AG51+AH51,"")</f>
         <v/>
       </c>
       <c r="AJ50" s="16" t="n"/>
@@ -5241,7 +5111,7 @@
       <c r="AG51" s="16" t="n"/>
       <c r="AH51" s="16" t="n"/>
       <c r="AI51" s="17">
-        <f>IFERROR(AF51+AG51+AH51,"")</f>
+        <f>IFERROR(AF52+AG52+AH52,"")</f>
         <v/>
       </c>
       <c r="AJ51" s="16" t="n"/>
@@ -5283,7 +5153,7 @@
       <c r="AG52" s="16" t="n"/>
       <c r="AH52" s="16" t="n"/>
       <c r="AI52" s="17">
-        <f>IFERROR(AF52+AG52+AH52,"")</f>
+        <f>IFERROR(AF53+AG53+AH53,"")</f>
         <v/>
       </c>
       <c r="AJ52" s="16" t="n"/>
@@ -5325,7 +5195,7 @@
       <c r="AG53" s="16" t="n"/>
       <c r="AH53" s="16" t="n"/>
       <c r="AI53" s="17">
-        <f>IFERROR(AF53+AG53+AH53,"")</f>
+        <f>IFERROR(AF54+AG54+AH54,"")</f>
         <v/>
       </c>
       <c r="AJ53" s="16" t="n"/>
@@ -5367,7 +5237,7 @@
       <c r="AG54" s="16" t="n"/>
       <c r="AH54" s="16" t="n"/>
       <c r="AI54" s="17">
-        <f>IFERROR(AF54+AG54+AH54,"")</f>
+        <f>IFERROR(AF55+AG55+AH55,"")</f>
         <v/>
       </c>
       <c r="AJ54" s="16" t="n"/>
@@ -5409,7 +5279,7 @@
       <c r="AG55" s="16" t="n"/>
       <c r="AH55" s="16" t="n"/>
       <c r="AI55" s="17">
-        <f>IFERROR(AF55+AG55+AH55,"")</f>
+        <f>IFERROR(AF56+AG56+AH56,"")</f>
         <v/>
       </c>
       <c r="AJ55" s="16" t="n"/>
@@ -5451,7 +5321,7 @@
       <c r="AG56" s="16" t="n"/>
       <c r="AH56" s="16" t="n"/>
       <c r="AI56" s="17">
-        <f>IFERROR(AF56+AG56+AH56,"")</f>
+        <f>IFERROR(AF57+AG57+AH57,"")</f>
         <v/>
       </c>
       <c r="AJ56" s="16" t="n"/>
@@ -5493,7 +5363,7 @@
       <c r="AG57" s="16" t="n"/>
       <c r="AH57" s="16" t="n"/>
       <c r="AI57" s="17">
-        <f>IFERROR(AF57+AG57+AH57,"")</f>
+        <f>IFERROR(AF58+AG58+AH58,"")</f>
         <v/>
       </c>
       <c r="AJ57" s="16" t="n"/>
@@ -5535,7 +5405,7 @@
       <c r="AG58" s="16" t="n"/>
       <c r="AH58" s="16" t="n"/>
       <c r="AI58" s="17">
-        <f>IFERROR(AF58+AG58+AH58,"")</f>
+        <f>IFERROR(AF59+AG59+AH59,"")</f>
         <v/>
       </c>
       <c r="AJ58" s="16" t="n"/>
@@ -5577,7 +5447,7 @@
       <c r="AG59" s="16" t="n"/>
       <c r="AH59" s="16" t="n"/>
       <c r="AI59" s="17">
-        <f>IFERROR(AF59+AG59+AH59,"")</f>
+        <f>IFERROR(AF60+AG60+AH60,"")</f>
         <v/>
       </c>
       <c r="AJ59" s="16" t="n"/>
@@ -5619,7 +5489,7 @@
       <c r="AG60" s="16" t="n"/>
       <c r="AH60" s="16" t="n"/>
       <c r="AI60" s="17">
-        <f>IFERROR(AF60+AG60+AH60,"")</f>
+        <f>IFERROR(AF61+AG61+AH61,"")</f>
         <v/>
       </c>
       <c r="AJ60" s="16" t="n"/>
@@ -5661,7 +5531,7 @@
       <c r="AG61" s="16" t="n"/>
       <c r="AH61" s="16" t="n"/>
       <c r="AI61" s="17">
-        <f>IFERROR(AF61+AG61+AH61,"")</f>
+        <f>IFERROR(AF62+AG62+AH62,"")</f>
         <v/>
       </c>
       <c r="AJ61" s="16" t="n"/>
@@ -5703,7 +5573,7 @@
       <c r="AG62" s="16" t="n"/>
       <c r="AH62" s="16" t="n"/>
       <c r="AI62" s="17">
-        <f>IFERROR(AF62+AG62+AH62,"")</f>
+        <f>IFERROR(AF63+AG63+AH63,"")</f>
         <v/>
       </c>
       <c r="AJ62" s="16" t="n"/>
@@ -5745,7 +5615,7 @@
       <c r="AG63" s="16" t="n"/>
       <c r="AH63" s="16" t="n"/>
       <c r="AI63" s="17">
-        <f>IFERROR(AF63+AG63+AH63,"")</f>
+        <f>IFERROR(AF64+AG64+AH64,"")</f>
         <v/>
       </c>
       <c r="AJ63" s="16" t="n"/>
@@ -5787,7 +5657,7 @@
       <c r="AG64" s="16" t="n"/>
       <c r="AH64" s="16" t="n"/>
       <c r="AI64" s="17">
-        <f>IFERROR(AF64+AG64+AH64,"")</f>
+        <f>IFERROR(AF65+AG65+AH65,"")</f>
         <v/>
       </c>
       <c r="AJ64" s="16" t="n"/>
@@ -5829,7 +5699,7 @@
       <c r="AG65" s="16" t="n"/>
       <c r="AH65" s="16" t="n"/>
       <c r="AI65" s="17">
-        <f>IFERROR(AF65+AG65+AH65,"")</f>
+        <f>IFERROR(AF66+AG66+AH66,"")</f>
         <v/>
       </c>
       <c r="AJ65" s="16" t="n"/>
@@ -5871,7 +5741,7 @@
       <c r="AG66" s="16" t="n"/>
       <c r="AH66" s="16" t="n"/>
       <c r="AI66" s="17">
-        <f>IFERROR(AF66+AG66+AH66,"")</f>
+        <f>IFERROR(AF67+AG67+AH67,"")</f>
         <v/>
       </c>
       <c r="AJ66" s="16" t="n"/>
@@ -5913,7 +5783,7 @@
       <c r="AG67" s="16" t="n"/>
       <c r="AH67" s="16" t="n"/>
       <c r="AI67" s="17">
-        <f>IFERROR(AF67+AG67+AH67,"")</f>
+        <f>IFERROR(AF68+AG68+AH68,"")</f>
         <v/>
       </c>
       <c r="AJ67" s="16" t="n"/>
@@ -5955,7 +5825,7 @@
       <c r="AG68" s="16" t="n"/>
       <c r="AH68" s="16" t="n"/>
       <c r="AI68" s="17">
-        <f>IFERROR(AF68+AG68+AH68,"")</f>
+        <f>IFERROR(AF69+AG69+AH69,"")</f>
         <v/>
       </c>
       <c r="AJ68" s="16" t="n"/>
@@ -5997,7 +5867,7 @@
       <c r="AG69" s="16" t="n"/>
       <c r="AH69" s="16" t="n"/>
       <c r="AI69" s="17">
-        <f>IFERROR(AF69+AG69+AH69,"")</f>
+        <f>IFERROR(AF70+AG70+AH70,"")</f>
         <v/>
       </c>
       <c r="AJ69" s="16" t="n"/>
@@ -6039,7 +5909,7 @@
       <c r="AG70" s="16" t="n"/>
       <c r="AH70" s="16" t="n"/>
       <c r="AI70" s="17">
-        <f>IFERROR(AF70+AG70+AH70,"")</f>
+        <f>IFERROR(AF71+AG71+AH71,"")</f>
         <v/>
       </c>
       <c r="AJ70" s="16" t="n"/>
@@ -6081,7 +5951,7 @@
       <c r="AG71" s="16" t="n"/>
       <c r="AH71" s="16" t="n"/>
       <c r="AI71" s="17">
-        <f>IFERROR(AF71+AG71+AH71,"")</f>
+        <f>IFERROR(AF72+AG72+AH72,"")</f>
         <v/>
       </c>
       <c r="AJ71" s="16" t="n"/>
@@ -6123,7 +5993,7 @@
       <c r="AG72" s="16" t="n"/>
       <c r="AH72" s="16" t="n"/>
       <c r="AI72" s="17">
-        <f>IFERROR(AF72+AG72+AH72,"")</f>
+        <f>IFERROR(AF73+AG73+AH73,"")</f>
         <v/>
       </c>
       <c r="AJ72" s="16" t="n"/>
@@ -6165,7 +6035,7 @@
       <c r="AG73" s="16" t="n"/>
       <c r="AH73" s="16" t="n"/>
       <c r="AI73" s="17">
-        <f>IFERROR(AF73+AG73+AH73,"")</f>
+        <f>IFERROR(AF74+AG74+AH74,"")</f>
         <v/>
       </c>
       <c r="AJ73" s="16" t="n"/>
@@ -6207,7 +6077,7 @@
       <c r="AG74" s="16" t="n"/>
       <c r="AH74" s="16" t="n"/>
       <c r="AI74" s="17">
-        <f>IFERROR(AF74+AG74+AH74,"")</f>
+        <f>IFERROR(AF75+AG75+AH75,"")</f>
         <v/>
       </c>
       <c r="AJ74" s="16" t="n"/>
@@ -6249,7 +6119,7 @@
       <c r="AG75" s="16" t="n"/>
       <c r="AH75" s="16" t="n"/>
       <c r="AI75" s="17">
-        <f>IFERROR(AF75+AG75+AH75,"")</f>
+        <f>IFERROR(AF76+AG76+AH76,"")</f>
         <v/>
       </c>
       <c r="AJ75" s="16" t="n"/>
@@ -6291,7 +6161,7 @@
       <c r="AG76" s="16" t="n"/>
       <c r="AH76" s="16" t="n"/>
       <c r="AI76" s="17">
-        <f>IFERROR(AF76+AG76+AH76,"")</f>
+        <f>IFERROR(AF77+AG77+AH77,"")</f>
         <v/>
       </c>
       <c r="AJ76" s="16" t="n"/>
@@ -6333,7 +6203,7 @@
       <c r="AG77" s="16" t="n"/>
       <c r="AH77" s="16" t="n"/>
       <c r="AI77" s="17">
-        <f>IFERROR(AF77+AG77+AH77,"")</f>
+        <f>IFERROR(AF78+AG78+AH78,"")</f>
         <v/>
       </c>
       <c r="AJ77" s="16" t="n"/>
@@ -6375,7 +6245,7 @@
       <c r="AG78" s="16" t="n"/>
       <c r="AH78" s="16" t="n"/>
       <c r="AI78" s="17">
-        <f>IFERROR(AF78+AG78+AH78,"")</f>
+        <f>IFERROR(AF79+AG79+AH79,"")</f>
         <v/>
       </c>
       <c r="AJ78" s="16" t="n"/>
@@ -6417,7 +6287,7 @@
       <c r="AG79" s="16" t="n"/>
       <c r="AH79" s="16" t="n"/>
       <c r="AI79" s="17">
-        <f>IFERROR(AF79+AG79+AH79,"")</f>
+        <f>IFERROR(AF80+AG80+AH80,"")</f>
         <v/>
       </c>
       <c r="AJ79" s="16" t="n"/>
@@ -6459,7 +6329,7 @@
       <c r="AG80" s="16" t="n"/>
       <c r="AH80" s="16" t="n"/>
       <c r="AI80" s="17">
-        <f>IFERROR(AF80+AG80+AH80,"")</f>
+        <f>IFERROR(AF81+AG81+AH81,"")</f>
         <v/>
       </c>
       <c r="AJ80" s="16" t="n"/>
@@ -6501,7 +6371,7 @@
       <c r="AG81" s="16" t="n"/>
       <c r="AH81" s="16" t="n"/>
       <c r="AI81" s="17">
-        <f>IFERROR(AF81+AG81+AH81,"")</f>
+        <f>IFERROR(AF82+AG82+AH82,"")</f>
         <v/>
       </c>
       <c r="AJ81" s="16" t="n"/>
@@ -6543,7 +6413,7 @@
       <c r="AG82" s="16" t="n"/>
       <c r="AH82" s="16" t="n"/>
       <c r="AI82" s="17">
-        <f>IFERROR(AF82+AG82+AH82,"")</f>
+        <f>IFERROR(AF83+AG83+AH83,"")</f>
         <v/>
       </c>
       <c r="AJ82" s="16" t="n"/>
@@ -6585,7 +6455,7 @@
       <c r="AG83" s="16" t="n"/>
       <c r="AH83" s="16" t="n"/>
       <c r="AI83" s="17">
-        <f>IFERROR(AF83+AG83+AH83,"")</f>
+        <f>IFERROR(AF84+AG84+AH84,"")</f>
         <v/>
       </c>
       <c r="AJ83" s="16" t="n"/>
@@ -6627,7 +6497,7 @@
       <c r="AG84" s="16" t="n"/>
       <c r="AH84" s="16" t="n"/>
       <c r="AI84" s="17">
-        <f>IFERROR(AF84+AG84+AH84,"")</f>
+        <f>IFERROR(AF85+AG85+AH85,"")</f>
         <v/>
       </c>
       <c r="AJ84" s="16" t="n"/>
@@ -6669,7 +6539,7 @@
       <c r="AG85" s="16" t="n"/>
       <c r="AH85" s="16" t="n"/>
       <c r="AI85" s="17">
-        <f>IFERROR(AF85+AG85+AH85,"")</f>
+        <f>IFERROR(AF86+AG86+AH86,"")</f>
         <v/>
       </c>
       <c r="AJ85" s="16" t="n"/>
@@ -6711,7 +6581,7 @@
       <c r="AG86" s="16" t="n"/>
       <c r="AH86" s="16" t="n"/>
       <c r="AI86" s="17">
-        <f>IFERROR(AF86+AG86+AH86,"")</f>
+        <f>IFERROR(AF87+AG87+AH87,"")</f>
         <v/>
       </c>
       <c r="AJ86" s="16" t="n"/>
@@ -6753,7 +6623,7 @@
       <c r="AG87" s="16" t="n"/>
       <c r="AH87" s="16" t="n"/>
       <c r="AI87" s="17">
-        <f>IFERROR(AF87+AG87+AH87,"")</f>
+        <f>IFERROR(AF88+AG88+AH88,"")</f>
         <v/>
       </c>
       <c r="AJ87" s="16" t="n"/>
@@ -6795,7 +6665,7 @@
       <c r="AG88" s="16" t="n"/>
       <c r="AH88" s="16" t="n"/>
       <c r="AI88" s="17">
-        <f>IFERROR(AF88+AG88+AH88,"")</f>
+        <f>IFERROR(AF89+AG89+AH89,"")</f>
         <v/>
       </c>
       <c r="AJ88" s="16" t="n"/>
@@ -6837,7 +6707,7 @@
       <c r="AG89" s="16" t="n"/>
       <c r="AH89" s="16" t="n"/>
       <c r="AI89" s="17">
-        <f>IFERROR(AF89+AG89+AH89,"")</f>
+        <f>IFERROR(AF90+AG90+AH90,"")</f>
         <v/>
       </c>
       <c r="AJ89" s="16" t="n"/>
@@ -6879,7 +6749,7 @@
       <c r="AG90" s="16" t="n"/>
       <c r="AH90" s="16" t="n"/>
       <c r="AI90" s="17">
-        <f>IFERROR(AF90+AG90+AH90,"")</f>
+        <f>IFERROR(AF91+AG91+AH91,"")</f>
         <v/>
       </c>
       <c r="AJ90" s="16" t="n"/>
@@ -6921,7 +6791,7 @@
       <c r="AG91" s="16" t="n"/>
       <c r="AH91" s="16" t="n"/>
       <c r="AI91" s="17">
-        <f>IFERROR(AF91+AG91+AH91,"")</f>
+        <f>IFERROR(AF92+AG92+AH92,"")</f>
         <v/>
       </c>
       <c r="AJ91" s="16" t="n"/>
@@ -6963,7 +6833,7 @@
       <c r="AG92" s="16" t="n"/>
       <c r="AH92" s="16" t="n"/>
       <c r="AI92" s="17">
-        <f>IFERROR(AF92+AG92+AH92,"")</f>
+        <f>IFERROR(AF93+AG93+AH93,"")</f>
         <v/>
       </c>
       <c r="AJ92" s="16" t="n"/>
@@ -7005,7 +6875,7 @@
       <c r="AG93" s="16" t="n"/>
       <c r="AH93" s="16" t="n"/>
       <c r="AI93" s="17">
-        <f>IFERROR(AF93+AG93+AH93,"")</f>
+        <f>IFERROR(AF94+AG94+AH94,"")</f>
         <v/>
       </c>
       <c r="AJ93" s="16" t="n"/>
@@ -7047,7 +6917,7 @@
       <c r="AG94" s="16" t="n"/>
       <c r="AH94" s="16" t="n"/>
       <c r="AI94" s="17">
-        <f>IFERROR(AF94+AG94+AH94,"")</f>
+        <f>IFERROR(AF95+AG95+AH95,"")</f>
         <v/>
       </c>
       <c r="AJ94" s="16" t="n"/>
@@ -7089,7 +6959,7 @@
       <c r="AG95" s="16" t="n"/>
       <c r="AH95" s="16" t="n"/>
       <c r="AI95" s="17">
-        <f>IFERROR(AF95+AG95+AH95,"")</f>
+        <f>IFERROR(AF96+AG96+AH96,"")</f>
         <v/>
       </c>
       <c r="AJ95" s="16" t="n"/>
@@ -7131,7 +7001,7 @@
       <c r="AG96" s="16" t="n"/>
       <c r="AH96" s="16" t="n"/>
       <c r="AI96" s="17">
-        <f>IFERROR(AF96+AG96+AH96,"")</f>
+        <f>IFERROR(AF97+AG97+AH97,"")</f>
         <v/>
       </c>
       <c r="AJ96" s="16" t="n"/>
@@ -7173,7 +7043,7 @@
       <c r="AG97" s="16" t="n"/>
       <c r="AH97" s="16" t="n"/>
       <c r="AI97" s="17">
-        <f>IFERROR(AF97+AG97+AH97,"")</f>
+        <f>IFERROR(AF98+AG98+AH98,"")</f>
         <v/>
       </c>
       <c r="AJ97" s="16" t="n"/>
@@ -7215,7 +7085,7 @@
       <c r="AG98" s="16" t="n"/>
       <c r="AH98" s="16" t="n"/>
       <c r="AI98" s="17">
-        <f>IFERROR(AF98+AG98+AH98,"")</f>
+        <f>IFERROR(AF99+AG99+AH99,"")</f>
         <v/>
       </c>
       <c r="AJ98" s="16" t="n"/>
@@ -7257,7 +7127,7 @@
       <c r="AG99" s="16" t="n"/>
       <c r="AH99" s="16" t="n"/>
       <c r="AI99" s="17">
-        <f>IFERROR(AF99+AG99+AH99,"")</f>
+        <f>IFERROR(AF100+AG100+AH100,"")</f>
         <v/>
       </c>
       <c r="AJ99" s="16" t="n"/>
@@ -7299,7 +7169,7 @@
       <c r="AG100" s="16" t="n"/>
       <c r="AH100" s="16" t="n"/>
       <c r="AI100" s="17">
-        <f>IFERROR(AF100+AG100+AH100,"")</f>
+        <f>IFERROR(AF101+AG101+AH101,"")</f>
         <v/>
       </c>
       <c r="AJ100" s="16" t="n"/>
@@ -7341,7 +7211,7 @@
       <c r="AG101" s="16" t="n"/>
       <c r="AH101" s="16" t="n"/>
       <c r="AI101" s="17">
-        <f>IFERROR(AF101+AG101+AH101,"")</f>
+        <f>IFERROR(AF102+AG102+AH102,"")</f>
         <v/>
       </c>
       <c r="AJ101" s="16" t="n"/>
@@ -7383,7 +7253,7 @@
       <c r="AG102" s="16" t="n"/>
       <c r="AH102" s="16" t="n"/>
       <c r="AI102" s="17">
-        <f>IFERROR(AF102+AG102+AH102,"")</f>
+        <f>IFERROR(AF103+AG103+AH103,"")</f>
         <v/>
       </c>
       <c r="AJ102" s="16" t="n"/>
@@ -7425,7 +7295,7 @@
       <c r="AG103" s="16" t="n"/>
       <c r="AH103" s="16" t="n"/>
       <c r="AI103" s="17">
-        <f>IFERROR(AF103+AG103+AH103,"")</f>
+        <f>IFERROR(AF104+AG104+AH104,"")</f>
         <v/>
       </c>
       <c r="AJ103" s="16" t="n"/>
@@ -7467,7 +7337,7 @@
       <c r="AG104" s="16" t="n"/>
       <c r="AH104" s="16" t="n"/>
       <c r="AI104" s="17">
-        <f>IFERROR(AF104+AG104+AH104,"")</f>
+        <f>IFERROR(AF105+AG105+AH105,"")</f>
         <v/>
       </c>
       <c r="AJ104" s="16" t="n"/>
@@ -7509,7 +7379,7 @@
       <c r="AG105" s="16" t="n"/>
       <c r="AH105" s="16" t="n"/>
       <c r="AI105" s="17">
-        <f>IFERROR(AF105+AG105+AH105,"")</f>
+        <f>IFERROR(AF106+AG106+AH106,"")</f>
         <v/>
       </c>
       <c r="AJ105" s="16" t="n"/>
@@ -7551,7 +7421,7 @@
       <c r="AG106" s="16" t="n"/>
       <c r="AH106" s="16" t="n"/>
       <c r="AI106" s="17">
-        <f>IFERROR(AF106+AG106+AH106,"")</f>
+        <f>IFERROR(AF107+AG107+AH107,"")</f>
         <v/>
       </c>
       <c r="AJ106" s="16" t="n"/>
@@ -7593,7 +7463,7 @@
       <c r="AG107" s="16" t="n"/>
       <c r="AH107" s="16" t="n"/>
       <c r="AI107" s="17">
-        <f>IFERROR(AF107+AG107+AH107,"")</f>
+        <f>IFERROR(AF108+AG108+AH108,"")</f>
         <v/>
       </c>
       <c r="AJ107" s="16" t="n"/>
@@ -7635,7 +7505,7 @@
       <c r="AG108" s="16" t="n"/>
       <c r="AH108" s="16" t="n"/>
       <c r="AI108" s="17">
-        <f>IFERROR(AF108+AG108+AH108,"")</f>
+        <f>IFERROR(AF109+AG109+AH109,"")</f>
         <v/>
       </c>
       <c r="AJ108" s="16" t="n"/>
@@ -7677,7 +7547,7 @@
       <c r="AG109" s="16" t="n"/>
       <c r="AH109" s="16" t="n"/>
       <c r="AI109" s="17">
-        <f>IFERROR(AF109+AG109+AH109,"")</f>
+        <f>IFERROR(AF110+AG110+AH110,"")</f>
         <v/>
       </c>
       <c r="AJ109" s="16" t="n"/>
@@ -7719,7 +7589,7 @@
       <c r="AG110" s="16" t="n"/>
       <c r="AH110" s="16" t="n"/>
       <c r="AI110" s="17">
-        <f>IFERROR(AF110+AG110+AH110,"")</f>
+        <f>IFERROR(AF111+AG111+AH111,"")</f>
         <v/>
       </c>
       <c r="AJ110" s="16" t="n"/>
@@ -7761,7 +7631,7 @@
       <c r="AG111" s="16" t="n"/>
       <c r="AH111" s="16" t="n"/>
       <c r="AI111" s="17">
-        <f>IFERROR(AF111+AG111+AH111,"")</f>
+        <f>IFERROR(AF112+AG112+AH112,"")</f>
         <v/>
       </c>
       <c r="AJ111" s="16" t="n"/>
@@ -7803,7 +7673,7 @@
       <c r="AG112" s="16" t="n"/>
       <c r="AH112" s="16" t="n"/>
       <c r="AI112" s="17">
-        <f>IFERROR(AF112+AG112+AH112,"")</f>
+        <f>IFERROR(AF113+AG113+AH113,"")</f>
         <v/>
       </c>
       <c r="AJ112" s="16" t="n"/>
@@ -7845,7 +7715,7 @@
       <c r="AG113" s="16" t="n"/>
       <c r="AH113" s="16" t="n"/>
       <c r="AI113" s="17">
-        <f>IFERROR(AF113+AG113+AH113,"")</f>
+        <f>IFERROR(AF114+AG114+AH114,"")</f>
         <v/>
       </c>
       <c r="AJ113" s="16" t="n"/>
@@ -7887,7 +7757,7 @@
       <c r="AG114" s="16" t="n"/>
       <c r="AH114" s="16" t="n"/>
       <c r="AI114" s="17">
-        <f>IFERROR(AF114+AG114+AH114,"")</f>
+        <f>IFERROR(AF115+AG115+AH115,"")</f>
         <v/>
       </c>
       <c r="AJ114" s="16" t="n"/>
@@ -7929,7 +7799,7 @@
       <c r="AG115" s="16" t="n"/>
       <c r="AH115" s="16" t="n"/>
       <c r="AI115" s="17">
-        <f>IFERROR(AF115+AG115+AH115,"")</f>
+        <f>IFERROR(AF116+AG116+AH116,"")</f>
         <v/>
       </c>
       <c r="AJ115" s="16" t="n"/>
@@ -7971,7 +7841,7 @@
       <c r="AG116" s="16" t="n"/>
       <c r="AH116" s="16" t="n"/>
       <c r="AI116" s="17">
-        <f>IFERROR(AF116+AG116+AH116,"")</f>
+        <f>IFERROR(AF117+AG117+AH117,"")</f>
         <v/>
       </c>
       <c r="AJ116" s="16" t="n"/>
@@ -8013,7 +7883,7 @@
       <c r="AG117" s="16" t="n"/>
       <c r="AH117" s="16" t="n"/>
       <c r="AI117" s="17">
-        <f>IFERROR(AF117+AG117+AH117,"")</f>
+        <f>IFERROR(AF118+AG118+AH118,"")</f>
         <v/>
       </c>
       <c r="AJ117" s="16" t="n"/>
@@ -8055,7 +7925,7 @@
       <c r="AG118" s="16" t="n"/>
       <c r="AH118" s="16" t="n"/>
       <c r="AI118" s="17">
-        <f>IFERROR(AF118+AG118+AH118,"")</f>
+        <f>IFERROR(AF119+AG119+AH119,"")</f>
         <v/>
       </c>
       <c r="AJ118" s="16" t="n"/>
@@ -8097,7 +7967,7 @@
       <c r="AG119" s="16" t="n"/>
       <c r="AH119" s="16" t="n"/>
       <c r="AI119" s="17">
-        <f>IFERROR(AF119+AG119+AH119,"")</f>
+        <f>IFERROR(AF120+AG120+AH120,"")</f>
         <v/>
       </c>
       <c r="AJ119" s="16" t="n"/>
@@ -8139,7 +8009,7 @@
       <c r="AG120" s="16" t="n"/>
       <c r="AH120" s="16" t="n"/>
       <c r="AI120" s="17">
-        <f>IFERROR(AF120+AG120+AH120,"")</f>
+        <f>IFERROR(AF121+AG121+AH121,"")</f>
         <v/>
       </c>
       <c r="AJ120" s="16" t="n"/>
@@ -8181,7 +8051,7 @@
       <c r="AG121" s="16" t="n"/>
       <c r="AH121" s="16" t="n"/>
       <c r="AI121" s="17">
-        <f>IFERROR(AF121+AG121+AH121,"")</f>
+        <f>IFERROR(AF122+AG122+AH122,"")</f>
         <v/>
       </c>
       <c r="AJ121" s="16" t="n"/>
@@ -8223,7 +8093,7 @@
       <c r="AG122" s="16" t="n"/>
       <c r="AH122" s="16" t="n"/>
       <c r="AI122" s="17">
-        <f>IFERROR(AF122+AG122+AH122,"")</f>
+        <f>IFERROR(AF123+AG123+AH123,"")</f>
         <v/>
       </c>
       <c r="AJ122" s="16" t="n"/>
@@ -8265,7 +8135,7 @@
       <c r="AG123" s="16" t="n"/>
       <c r="AH123" s="16" t="n"/>
       <c r="AI123" s="17">
-        <f>IFERROR(AF123+AG123+AH123,"")</f>
+        <f>IFERROR(AF124+AG124+AH124,"")</f>
         <v/>
       </c>
       <c r="AJ123" s="16" t="n"/>
@@ -8307,7 +8177,7 @@
       <c r="AG124" s="16" t="n"/>
       <c r="AH124" s="16" t="n"/>
       <c r="AI124" s="17">
-        <f>IFERROR(AF124+AG124+AH124,"")</f>
+        <f>IFERROR(AF125+AG125+AH125,"")</f>
         <v/>
       </c>
       <c r="AJ124" s="16" t="n"/>
@@ -8349,7 +8219,7 @@
       <c r="AG125" s="16" t="n"/>
       <c r="AH125" s="16" t="n"/>
       <c r="AI125" s="17">
-        <f>IFERROR(AF125+AG125+AH125,"")</f>
+        <f>IFERROR(AF126+AG126+AH126,"")</f>
         <v/>
       </c>
       <c r="AJ125" s="16" t="n"/>
@@ -8391,7 +8261,7 @@
       <c r="AG126" s="16" t="n"/>
       <c r="AH126" s="16" t="n"/>
       <c r="AI126" s="17">
-        <f>IFERROR(AF126+AG126+AH126,"")</f>
+        <f>IFERROR(AF127+AG127+AH127,"")</f>
         <v/>
       </c>
       <c r="AJ126" s="16" t="n"/>
@@ -8433,7 +8303,7 @@
       <c r="AG127" s="16" t="n"/>
       <c r="AH127" s="16" t="n"/>
       <c r="AI127" s="17">
-        <f>IFERROR(AF127+AG127+AH127,"")</f>
+        <f>IFERROR(AF128+AG128+AH128,"")</f>
         <v/>
       </c>
       <c r="AJ127" s="16" t="n"/>
@@ -8475,7 +8345,7 @@
       <c r="AG128" s="16" t="n"/>
       <c r="AH128" s="16" t="n"/>
       <c r="AI128" s="17">
-        <f>IFERROR(AF128+AG128+AH128,"")</f>
+        <f>IFERROR(AF129+AG129+AH129,"")</f>
         <v/>
       </c>
       <c r="AJ128" s="16" t="n"/>
@@ -8517,7 +8387,7 @@
       <c r="AG129" s="16" t="n"/>
       <c r="AH129" s="16" t="n"/>
       <c r="AI129" s="17">
-        <f>IFERROR(AF129+AG129+AH129,"")</f>
+        <f>IFERROR(AF130+AG130+AH130,"")</f>
         <v/>
       </c>
       <c r="AJ129" s="16" t="n"/>
@@ -8559,7 +8429,7 @@
       <c r="AG130" s="16" t="n"/>
       <c r="AH130" s="16" t="n"/>
       <c r="AI130" s="17">
-        <f>IFERROR(AF130+AG130+AH130,"")</f>
+        <f>IFERROR(AF131+AG131+AH131,"")</f>
         <v/>
       </c>
       <c r="AJ130" s="16" t="n"/>
@@ -8601,7 +8471,7 @@
       <c r="AG131" s="16" t="n"/>
       <c r="AH131" s="16" t="n"/>
       <c r="AI131" s="17">
-        <f>IFERROR(AF131+AG131+AH131,"")</f>
+        <f>IFERROR(AF132+AG132+AH132,"")</f>
         <v/>
       </c>
       <c r="AJ131" s="16" t="n"/>
@@ -8643,7 +8513,7 @@
       <c r="AG132" s="16" t="n"/>
       <c r="AH132" s="16" t="n"/>
       <c r="AI132" s="17">
-        <f>IFERROR(AF132+AG132+AH132,"")</f>
+        <f>IFERROR(AF133+AG133+AH133,"")</f>
         <v/>
       </c>
       <c r="AJ132" s="16" t="n"/>
@@ -8685,7 +8555,7 @@
       <c r="AG133" s="16" t="n"/>
       <c r="AH133" s="16" t="n"/>
       <c r="AI133" s="17">
-        <f>IFERROR(AF133+AG133+AH133,"")</f>
+        <f>IFERROR(AF134+AG134+AH134,"")</f>
         <v/>
       </c>
       <c r="AJ133" s="16" t="n"/>
@@ -8727,7 +8597,7 @@
       <c r="AG134" s="16" t="n"/>
       <c r="AH134" s="16" t="n"/>
       <c r="AI134" s="17">
-        <f>IFERROR(AF134+AG134+AH134,"")</f>
+        <f>IFERROR(AF135+AG135+AH135,"")</f>
         <v/>
       </c>
       <c r="AJ134" s="16" t="n"/>
@@ -8769,7 +8639,7 @@
       <c r="AG135" s="16" t="n"/>
       <c r="AH135" s="16" t="n"/>
       <c r="AI135" s="17">
-        <f>IFERROR(AF135+AG135+AH135,"")</f>
+        <f>IFERROR(AF136+AG136+AH136,"")</f>
         <v/>
       </c>
       <c r="AJ135" s="16" t="n"/>
@@ -8811,7 +8681,7 @@
       <c r="AG136" s="16" t="n"/>
       <c r="AH136" s="16" t="n"/>
       <c r="AI136" s="17">
-        <f>IFERROR(AF136+AG136+AH136,"")</f>
+        <f>IFERROR(AF137+AG137+AH137,"")</f>
         <v/>
       </c>
       <c r="AJ136" s="16" t="n"/>
@@ -8853,7 +8723,7 @@
       <c r="AG137" s="16" t="n"/>
       <c r="AH137" s="16" t="n"/>
       <c r="AI137" s="17">
-        <f>IFERROR(AF137+AG137+AH137,"")</f>
+        <f>IFERROR(AF138+AG138+AH138,"")</f>
         <v/>
       </c>
       <c r="AJ137" s="16" t="n"/>
@@ -8895,7 +8765,7 @@
       <c r="AG138" s="16" t="n"/>
       <c r="AH138" s="16" t="n"/>
       <c r="AI138" s="17">
-        <f>IFERROR(AF138+AG138+AH138,"")</f>
+        <f>IFERROR(AF139+AG139+AH139,"")</f>
         <v/>
       </c>
       <c r="AJ138" s="16" t="n"/>
@@ -8937,7 +8807,7 @@
       <c r="AG139" s="16" t="n"/>
       <c r="AH139" s="16" t="n"/>
       <c r="AI139" s="17">
-        <f>IFERROR(AF139+AG139+AH139,"")</f>
+        <f>IFERROR(AF140+AG140+AH140,"")</f>
         <v/>
       </c>
       <c r="AJ139" s="16" t="n"/>
@@ -8979,7 +8849,7 @@
       <c r="AG140" s="16" t="n"/>
       <c r="AH140" s="16" t="n"/>
       <c r="AI140" s="17">
-        <f>IFERROR(AF140+AG140+AH140,"")</f>
+        <f>IFERROR(AF141+AG141+AH141,"")</f>
         <v/>
       </c>
       <c r="AJ140" s="16" t="n"/>
@@ -9021,7 +8891,7 @@
       <c r="AG141" s="16" t="n"/>
       <c r="AH141" s="16" t="n"/>
       <c r="AI141" s="17">
-        <f>IFERROR(AF141+AG141+AH141,"")</f>
+        <f>IFERROR(AF142+AG142+AH142,"")</f>
         <v/>
       </c>
       <c r="AJ141" s="16" t="n"/>
@@ -9063,7 +8933,7 @@
       <c r="AG142" s="16" t="n"/>
       <c r="AH142" s="16" t="n"/>
       <c r="AI142" s="17">
-        <f>IFERROR(AF142+AG142+AH142,"")</f>
+        <f>IFERROR(AF143+AG143+AH143,"")</f>
         <v/>
       </c>
       <c r="AJ142" s="16" t="n"/>
@@ -9105,7 +8975,7 @@
       <c r="AG143" s="16" t="n"/>
       <c r="AH143" s="16" t="n"/>
       <c r="AI143" s="17">
-        <f>IFERROR(AF143+AG143+AH143,"")</f>
+        <f>IFERROR(AF144+AG144+AH144,"")</f>
         <v/>
       </c>
       <c r="AJ143" s="16" t="n"/>
@@ -9147,7 +9017,7 @@
       <c r="AG144" s="16" t="n"/>
       <c r="AH144" s="16" t="n"/>
       <c r="AI144" s="17">
-        <f>IFERROR(AF144+AG144+AH144,"")</f>
+        <f>IFERROR(AF145+AG145+AH145,"")</f>
         <v/>
       </c>
       <c r="AJ144" s="16" t="n"/>
@@ -9189,7 +9059,7 @@
       <c r="AG145" s="16" t="n"/>
       <c r="AH145" s="16" t="n"/>
       <c r="AI145" s="17">
-        <f>IFERROR(AF145+AG145+AH145,"")</f>
+        <f>IFERROR(AF146+AG146+AH146,"")</f>
         <v/>
       </c>
       <c r="AJ145" s="16" t="n"/>
@@ -9231,7 +9101,7 @@
       <c r="AG146" s="16" t="n"/>
       <c r="AH146" s="16" t="n"/>
       <c r="AI146" s="17">
-        <f>IFERROR(AF146+AG146+AH146,"")</f>
+        <f>IFERROR(AF147+AG147+AH147,"")</f>
         <v/>
       </c>
       <c r="AJ146" s="16" t="n"/>
@@ -9273,7 +9143,7 @@
       <c r="AG147" s="16" t="n"/>
       <c r="AH147" s="16" t="n"/>
       <c r="AI147" s="17">
-        <f>IFERROR(AF147+AG147+AH147,"")</f>
+        <f>IFERROR(AF148+AG148+AH148,"")</f>
         <v/>
       </c>
       <c r="AJ147" s="16" t="n"/>
@@ -9315,7 +9185,7 @@
       <c r="AG148" s="16" t="n"/>
       <c r="AH148" s="16" t="n"/>
       <c r="AI148" s="17">
-        <f>IFERROR(AF148+AG148+AH148,"")</f>
+        <f>IFERROR(AF149+AG149+AH149,"")</f>
         <v/>
       </c>
       <c r="AJ148" s="16" t="n"/>
@@ -9357,7 +9227,7 @@
       <c r="AG149" s="16" t="n"/>
       <c r="AH149" s="16" t="n"/>
       <c r="AI149" s="17">
-        <f>IFERROR(AF149+AG149+AH149,"")</f>
+        <f>IFERROR(AF150+AG150+AH150,"")</f>
         <v/>
       </c>
       <c r="AJ149" s="16" t="n"/>
@@ -9399,7 +9269,7 @@
       <c r="AG150" s="16" t="n"/>
       <c r="AH150" s="16" t="n"/>
       <c r="AI150" s="17">
-        <f>IFERROR(AF150+AG150+AH150,"")</f>
+        <f>IFERROR(AF151+AG151+AH151,"")</f>
         <v/>
       </c>
       <c r="AJ150" s="16" t="n"/>
@@ -9441,7 +9311,7 @@
       <c r="AG151" s="16" t="n"/>
       <c r="AH151" s="16" t="n"/>
       <c r="AI151" s="17">
-        <f>IFERROR(AF151+AG151+AH151,"")</f>
+        <f>IFERROR(AF152+AG152+AH152,"")</f>
         <v/>
       </c>
       <c r="AJ151" s="16" t="n"/>
@@ -9483,7 +9353,7 @@
       <c r="AG152" s="16" t="n"/>
       <c r="AH152" s="16" t="n"/>
       <c r="AI152" s="17">
-        <f>IFERROR(AF152+AG152+AH152,"")</f>
+        <f>IFERROR(AF153+AG153+AH153,"")</f>
         <v/>
       </c>
       <c r="AJ152" s="16" t="n"/>
@@ -9525,7 +9395,7 @@
       <c r="AG153" s="16" t="n"/>
       <c r="AH153" s="16" t="n"/>
       <c r="AI153" s="17">
-        <f>IFERROR(AF153+AG153+AH153,"")</f>
+        <f>IFERROR(AF154+AG154+AH154,"")</f>
         <v/>
       </c>
       <c r="AJ153" s="16" t="n"/>
@@ -9567,7 +9437,7 @@
       <c r="AG154" s="16" t="n"/>
       <c r="AH154" s="16" t="n"/>
       <c r="AI154" s="17">
-        <f>IFERROR(AF154+AG154+AH154,"")</f>
+        <f>IFERROR(AF155+AG155+AH155,"")</f>
         <v/>
       </c>
       <c r="AJ154" s="16" t="n"/>
@@ -9609,7 +9479,7 @@
       <c r="AG155" s="16" t="n"/>
       <c r="AH155" s="16" t="n"/>
       <c r="AI155" s="17">
-        <f>IFERROR(AF155+AG155+AH155,"")</f>
+        <f>IFERROR(AF156+AG156+AH156,"")</f>
         <v/>
       </c>
       <c r="AJ155" s="16" t="n"/>
@@ -9651,7 +9521,7 @@
       <c r="AG156" s="16" t="n"/>
       <c r="AH156" s="16" t="n"/>
       <c r="AI156" s="17">
-        <f>IFERROR(AF156+AG156+AH156,"")</f>
+        <f>IFERROR(AF157+AG157+AH157,"")</f>
         <v/>
       </c>
       <c r="AJ156" s="16" t="n"/>
@@ -9693,7 +9563,7 @@
       <c r="AG157" s="16" t="n"/>
       <c r="AH157" s="16" t="n"/>
       <c r="AI157" s="17">
-        <f>IFERROR(AF157+AG157+AH157,"")</f>
+        <f>IFERROR(AF158+AG158+AH158,"")</f>
         <v/>
       </c>
       <c r="AJ157" s="16" t="n"/>
@@ -9735,7 +9605,7 @@
       <c r="AG158" s="16" t="n"/>
       <c r="AH158" s="16" t="n"/>
       <c r="AI158" s="17">
-        <f>IFERROR(AF158+AG158+AH158,"")</f>
+        <f>IFERROR(AF159+AG159+AH159,"")</f>
         <v/>
       </c>
       <c r="AJ158" s="16" t="n"/>
@@ -9777,7 +9647,7 @@
       <c r="AG159" s="16" t="n"/>
       <c r="AH159" s="16" t="n"/>
       <c r="AI159" s="17">
-        <f>IFERROR(AF159+AG159+AH159,"")</f>
+        <f>IFERROR(AF160+AG160+AH160,"")</f>
         <v/>
       </c>
       <c r="AJ159" s="16" t="n"/>
@@ -9819,7 +9689,7 @@
       <c r="AG160" s="16" t="n"/>
       <c r="AH160" s="16" t="n"/>
       <c r="AI160" s="17">
-        <f>IFERROR(AF160+AG160+AH160,"")</f>
+        <f>IFERROR(AF161+AG161+AH161,"")</f>
         <v/>
       </c>
       <c r="AJ160" s="16" t="n"/>
@@ -9861,7 +9731,7 @@
       <c r="AG161" s="16" t="n"/>
       <c r="AH161" s="16" t="n"/>
       <c r="AI161" s="17">
-        <f>IFERROR(AF161+AG161+AH161,"")</f>
+        <f>IFERROR(AF162+AG162+AH162,"")</f>
         <v/>
       </c>
       <c r="AJ161" s="16" t="n"/>
@@ -9903,7 +9773,7 @@
       <c r="AG162" s="16" t="n"/>
       <c r="AH162" s="16" t="n"/>
       <c r="AI162" s="17">
-        <f>IFERROR(AF162+AG162+AH162,"")</f>
+        <f>IFERROR(AF163+AG163+AH163,"")</f>
         <v/>
       </c>
       <c r="AJ162" s="16" t="n"/>
@@ -9945,7 +9815,7 @@
       <c r="AG163" s="16" t="n"/>
       <c r="AH163" s="16" t="n"/>
       <c r="AI163" s="17">
-        <f>IFERROR(AF163+AG163+AH163,"")</f>
+        <f>IFERROR(AF164+AG164+AH164,"")</f>
         <v/>
       </c>
       <c r="AJ163" s="16" t="n"/>
@@ -9987,7 +9857,7 @@
       <c r="AG164" s="16" t="n"/>
       <c r="AH164" s="16" t="n"/>
       <c r="AI164" s="17">
-        <f>IFERROR(AF164+AG164+AH164,"")</f>
+        <f>IFERROR(AF165+AG165+AH165,"")</f>
         <v/>
       </c>
       <c r="AJ164" s="16" t="n"/>
@@ -10029,7 +9899,7 @@
       <c r="AG165" s="16" t="n"/>
       <c r="AH165" s="16" t="n"/>
       <c r="AI165" s="17">
-        <f>IFERROR(AF165+AG165+AH165,"")</f>
+        <f>IFERROR(AF166+AG166+AH166,"")</f>
         <v/>
       </c>
       <c r="AJ165" s="16" t="n"/>
@@ -10071,7 +9941,7 @@
       <c r="AG166" s="16" t="n"/>
       <c r="AH166" s="16" t="n"/>
       <c r="AI166" s="17">
-        <f>IFERROR(AF166+AG166+AH166,"")</f>
+        <f>IFERROR(AF167+AG167+AH167,"")</f>
         <v/>
       </c>
       <c r="AJ166" s="16" t="n"/>
@@ -10113,7 +9983,7 @@
       <c r="AG167" s="16" t="n"/>
       <c r="AH167" s="16" t="n"/>
       <c r="AI167" s="17">
-        <f>IFERROR(AF167+AG167+AH167,"")</f>
+        <f>IFERROR(AF168+AG168+AH168,"")</f>
         <v/>
       </c>
       <c r="AJ167" s="16" t="n"/>
@@ -10155,7 +10025,7 @@
       <c r="AG168" s="16" t="n"/>
       <c r="AH168" s="16" t="n"/>
       <c r="AI168" s="17">
-        <f>IFERROR(AF168+AG168+AH168,"")</f>
+        <f>IFERROR(AF169+AG169+AH169,"")</f>
         <v/>
       </c>
       <c r="AJ168" s="16" t="n"/>
@@ -10197,7 +10067,7 @@
       <c r="AG169" s="16" t="n"/>
       <c r="AH169" s="16" t="n"/>
       <c r="AI169" s="17">
-        <f>IFERROR(AF169+AG169+AH169,"")</f>
+        <f>IFERROR(AF170+AG170+AH170,"")</f>
         <v/>
       </c>
       <c r="AJ169" s="16" t="n"/>
@@ -10239,7 +10109,7 @@
       <c r="AG170" s="16" t="n"/>
       <c r="AH170" s="16" t="n"/>
       <c r="AI170" s="17">
-        <f>IFERROR(AF170+AG170+AH170,"")</f>
+        <f>IFERROR(AF171+AG171+AH171,"")</f>
         <v/>
       </c>
       <c r="AJ170" s="16" t="n"/>
@@ -10281,7 +10151,7 @@
       <c r="AG171" s="16" t="n"/>
       <c r="AH171" s="16" t="n"/>
       <c r="AI171" s="17">
-        <f>IFERROR(AF171+AG171+AH171,"")</f>
+        <f>IFERROR(AF172+AG172+AH172,"")</f>
         <v/>
       </c>
       <c r="AJ171" s="16" t="n"/>
@@ -10323,7 +10193,7 @@
       <c r="AG172" s="16" t="n"/>
       <c r="AH172" s="16" t="n"/>
       <c r="AI172" s="17">
-        <f>IFERROR(AF172+AG172+AH172,"")</f>
+        <f>IFERROR(AF173+AG173+AH173,"")</f>
         <v/>
       </c>
       <c r="AJ172" s="16" t="n"/>
@@ -10365,7 +10235,7 @@
       <c r="AG173" s="16" t="n"/>
       <c r="AH173" s="16" t="n"/>
       <c r="AI173" s="17">
-        <f>IFERROR(AF173+AG173+AH173,"")</f>
+        <f>IFERROR(AF174+AG174+AH174,"")</f>
         <v/>
       </c>
       <c r="AJ173" s="16" t="n"/>
@@ -10407,7 +10277,7 @@
       <c r="AG174" s="16" t="n"/>
       <c r="AH174" s="16" t="n"/>
       <c r="AI174" s="17">
-        <f>IFERROR(AF174+AG174+AH174,"")</f>
+        <f>IFERROR(AF175+AG175+AH175,"")</f>
         <v/>
       </c>
       <c r="AJ174" s="16" t="n"/>
@@ -10449,7 +10319,7 @@
       <c r="AG175" s="16" t="n"/>
       <c r="AH175" s="16" t="n"/>
       <c r="AI175" s="17">
-        <f>IFERROR(AF175+AG175+AH175,"")</f>
+        <f>IFERROR(AF176+AG176+AH176,"")</f>
         <v/>
       </c>
       <c r="AJ175" s="16" t="n"/>
@@ -10491,7 +10361,7 @@
       <c r="AG176" s="16" t="n"/>
       <c r="AH176" s="16" t="n"/>
       <c r="AI176" s="17">
-        <f>IFERROR(AF176+AG176+AH176,"")</f>
+        <f>IFERROR(AF177+AG177+AH177,"")</f>
         <v/>
       </c>
       <c r="AJ176" s="16" t="n"/>
@@ -10533,7 +10403,7 @@
       <c r="AG177" s="16" t="n"/>
       <c r="AH177" s="16" t="n"/>
       <c r="AI177" s="17">
-        <f>IFERROR(AF177+AG177+AH177,"")</f>
+        <f>IFERROR(AF178+AG178+AH178,"")</f>
         <v/>
       </c>
       <c r="AJ177" s="16" t="n"/>
@@ -10575,7 +10445,7 @@
       <c r="AG178" s="16" t="n"/>
       <c r="AH178" s="16" t="n"/>
       <c r="AI178" s="17">
-        <f>IFERROR(AF178+AG178+AH178,"")</f>
+        <f>IFERROR(AF179+AG179+AH179,"")</f>
         <v/>
       </c>
       <c r="AJ178" s="16" t="n"/>
@@ -10617,7 +10487,7 @@
       <c r="AG179" s="16" t="n"/>
       <c r="AH179" s="16" t="n"/>
       <c r="AI179" s="17">
-        <f>IFERROR(AF179+AG179+AH179,"")</f>
+        <f>IFERROR(AF180+AG180+AH180,"")</f>
         <v/>
       </c>
       <c r="AJ179" s="16" t="n"/>
@@ -10659,7 +10529,7 @@
       <c r="AG180" s="16" t="n"/>
       <c r="AH180" s="16" t="n"/>
       <c r="AI180" s="17">
-        <f>IFERROR(AF180+AG180+AH180,"")</f>
+        <f>IFERROR(AF181+AG181+AH181,"")</f>
         <v/>
       </c>
       <c r="AJ180" s="16" t="n"/>
@@ -10701,7 +10571,7 @@
       <c r="AG181" s="16" t="n"/>
       <c r="AH181" s="16" t="n"/>
       <c r="AI181" s="17">
-        <f>IFERROR(AF181+AG181+AH181,"")</f>
+        <f>IFERROR(AF182+AG182+AH182,"")</f>
         <v/>
       </c>
       <c r="AJ181" s="16" t="n"/>
@@ -10743,7 +10613,7 @@
       <c r="AG182" s="16" t="n"/>
       <c r="AH182" s="16" t="n"/>
       <c r="AI182" s="17">
-        <f>IFERROR(AF182+AG182+AH182,"")</f>
+        <f>IFERROR(AF183+AG183+AH183,"")</f>
         <v/>
       </c>
       <c r="AJ182" s="16" t="n"/>
@@ -10785,7 +10655,7 @@
       <c r="AG183" s="16" t="n"/>
       <c r="AH183" s="16" t="n"/>
       <c r="AI183" s="17">
-        <f>IFERROR(AF183+AG183+AH183,"")</f>
+        <f>IFERROR(AF184+AG184+AH184,"")</f>
         <v/>
       </c>
       <c r="AJ183" s="16" t="n"/>
@@ -10827,7 +10697,7 @@
       <c r="AG184" s="16" t="n"/>
       <c r="AH184" s="16" t="n"/>
       <c r="AI184" s="17">
-        <f>IFERROR(AF184+AG184+AH184,"")</f>
+        <f>IFERROR(AF185+AG185+AH185,"")</f>
         <v/>
       </c>
       <c r="AJ184" s="16" t="n"/>
@@ -10869,7 +10739,7 @@
       <c r="AG185" s="16" t="n"/>
       <c r="AH185" s="16" t="n"/>
       <c r="AI185" s="17">
-        <f>IFERROR(AF185+AG185+AH185,"")</f>
+        <f>IFERROR(AF186+AG186+AH186,"")</f>
         <v/>
       </c>
       <c r="AJ185" s="16" t="n"/>
@@ -10911,7 +10781,7 @@
       <c r="AG186" s="16" t="n"/>
       <c r="AH186" s="16" t="n"/>
       <c r="AI186" s="17">
-        <f>IFERROR(AF186+AG186+AH186,"")</f>
+        <f>IFERROR(AF187+AG187+AH187,"")</f>
         <v/>
       </c>
       <c r="AJ186" s="16" t="n"/>
@@ -10953,7 +10823,7 @@
       <c r="AG187" s="16" t="n"/>
       <c r="AH187" s="16" t="n"/>
       <c r="AI187" s="17">
-        <f>IFERROR(AF187+AG187+AH187,"")</f>
+        <f>IFERROR(AF188+AG188+AH188,"")</f>
         <v/>
       </c>
       <c r="AJ187" s="16" t="n"/>
@@ -10995,7 +10865,7 @@
       <c r="AG188" s="16" t="n"/>
       <c r="AH188" s="16" t="n"/>
       <c r="AI188" s="17">
-        <f>IFERROR(AF188+AG188+AH188,"")</f>
+        <f>IFERROR(AF189+AG189+AH189,"")</f>
         <v/>
       </c>
       <c r="AJ188" s="16" t="n"/>
@@ -11037,7 +10907,7 @@
       <c r="AG189" s="16" t="n"/>
       <c r="AH189" s="16" t="n"/>
       <c r="AI189" s="17">
-        <f>IFERROR(AF189+AG189+AH189,"")</f>
+        <f>IFERROR(AF190+AG190+AH190,"")</f>
         <v/>
       </c>
       <c r="AJ189" s="16" t="n"/>
@@ -11079,7 +10949,7 @@
       <c r="AG190" s="16" t="n"/>
       <c r="AH190" s="16" t="n"/>
       <c r="AI190" s="17">
-        <f>IFERROR(AF190+AG190+AH190,"")</f>
+        <f>IFERROR(AF191+AG191+AH191,"")</f>
         <v/>
       </c>
       <c r="AJ190" s="16" t="n"/>
@@ -11121,7 +10991,7 @@
       <c r="AG191" s="16" t="n"/>
       <c r="AH191" s="16" t="n"/>
       <c r="AI191" s="17">
-        <f>IFERROR(AF191+AG191+AH191,"")</f>
+        <f>IFERROR(AF192+AG192+AH192,"")</f>
         <v/>
       </c>
       <c r="AJ191" s="16" t="n"/>
@@ -11163,7 +11033,7 @@
       <c r="AG192" s="16" t="n"/>
       <c r="AH192" s="16" t="n"/>
       <c r="AI192" s="17">
-        <f>IFERROR(AF192+AG192+AH192,"")</f>
+        <f>IFERROR(AF193+AG193+AH193,"")</f>
         <v/>
       </c>
       <c r="AJ192" s="16" t="n"/>
@@ -11205,7 +11075,7 @@
       <c r="AG193" s="16" t="n"/>
       <c r="AH193" s="16" t="n"/>
       <c r="AI193" s="17">
-        <f>IFERROR(AF193+AG193+AH193,"")</f>
+        <f>IFERROR(AF194+AG194+AH194,"")</f>
         <v/>
       </c>
       <c r="AJ193" s="16" t="n"/>
@@ -11247,7 +11117,7 @@
       <c r="AG194" s="16" t="n"/>
       <c r="AH194" s="16" t="n"/>
       <c r="AI194" s="17">
-        <f>IFERROR(AF194+AG194+AH194,"")</f>
+        <f>IFERROR(AF195+AG195+AH195,"")</f>
         <v/>
       </c>
       <c r="AJ194" s="16" t="n"/>
@@ -11289,7 +11159,7 @@
       <c r="AG195" s="16" t="n"/>
       <c r="AH195" s="16" t="n"/>
       <c r="AI195" s="17">
-        <f>IFERROR(AF195+AG195+AH195,"")</f>
+        <f>IFERROR(AF196+AG196+AH196,"")</f>
         <v/>
       </c>
       <c r="AJ195" s="16" t="n"/>
@@ -11331,7 +11201,7 @@
       <c r="AG196" s="16" t="n"/>
       <c r="AH196" s="16" t="n"/>
       <c r="AI196" s="17">
-        <f>IFERROR(AF196+AG196+AH196,"")</f>
+        <f>IFERROR(AF197+AG197+AH197,"")</f>
         <v/>
       </c>
       <c r="AJ196" s="16" t="n"/>
@@ -11373,7 +11243,7 @@
       <c r="AG197" s="16" t="n"/>
       <c r="AH197" s="16" t="n"/>
       <c r="AI197" s="17">
-        <f>IFERROR(AF197+AG197+AH197,"")</f>
+        <f>IFERROR(AF198+AG198+AH198,"")</f>
         <v/>
       </c>
       <c r="AJ197" s="16" t="n"/>
@@ -11415,7 +11285,7 @@
       <c r="AG198" s="16" t="n"/>
       <c r="AH198" s="16" t="n"/>
       <c r="AI198" s="17">
-        <f>IFERROR(AF198+AG198+AH198,"")</f>
+        <f>IFERROR(AF199+AG199+AH199,"")</f>
         <v/>
       </c>
       <c r="AJ198" s="16" t="n"/>
@@ -11457,7 +11327,7 @@
       <c r="AG199" s="16" t="n"/>
       <c r="AH199" s="16" t="n"/>
       <c r="AI199" s="17">
-        <f>IFERROR(AF199+AG199+AH199,"")</f>
+        <f>IFERROR(AF200+AG200+AH200,"")</f>
         <v/>
       </c>
       <c r="AJ199" s="16" t="n"/>
@@ -11499,7 +11369,7 @@
       <c r="AG200" s="16" t="n"/>
       <c r="AH200" s="16" t="n"/>
       <c r="AI200" s="17">
-        <f>IFERROR(AF200+AG200+AH200,"")</f>
+        <f>IFERROR(AF201+AG201+AH201,"")</f>
         <v/>
       </c>
       <c r="AJ200" s="16" t="n"/>
@@ -11541,7 +11411,7 @@
       <c r="AG201" s="16" t="n"/>
       <c r="AH201" s="16" t="n"/>
       <c r="AI201" s="17">
-        <f>IFERROR(AF201+AG201+AH201,"")</f>
+        <f>IFERROR(AF202+AG202+AH202,"")</f>
         <v/>
       </c>
       <c r="AJ201" s="16" t="n"/>
@@ -11583,54 +11453,13 @@
       <c r="AG202" s="16" t="n"/>
       <c r="AH202" s="16" t="n"/>
       <c r="AI202" s="17">
-        <f>IFERROR(AF202+AG202+AH202,"")</f>
+        <f>IFERROR(AF203+AG203+AH203,"")</f>
         <v/>
       </c>
       <c r="AJ202" s="16" t="n"/>
       <c r="AK202" s="16" t="n"/>
     </row>
-    <row r="203" ht="18" customHeight="1">
-      <c r="A203" s="16" t="n"/>
-      <c r="B203" s="16" t="n"/>
-      <c r="C203" s="16" t="n"/>
-      <c r="D203" s="16" t="n"/>
-      <c r="E203" s="16" t="n"/>
-      <c r="F203" s="16" t="n"/>
-      <c r="G203" s="16" t="n"/>
-      <c r="H203" s="16" t="n"/>
-      <c r="I203" s="16" t="n"/>
-      <c r="J203" s="16" t="n"/>
-      <c r="K203" s="16" t="n"/>
-      <c r="L203" s="16" t="n"/>
-      <c r="M203" s="16" t="n"/>
-      <c r="N203" s="16" t="n"/>
-      <c r="O203" s="16" t="n"/>
-      <c r="P203" s="16" t="n"/>
-      <c r="Q203" s="16" t="n"/>
-      <c r="R203" s="16" t="n"/>
-      <c r="S203" s="16" t="n"/>
-      <c r="T203" s="16" t="n"/>
-      <c r="U203" s="16" t="n"/>
-      <c r="V203" s="16" t="n"/>
-      <c r="W203" s="16" t="n"/>
-      <c r="X203" s="16" t="n"/>
-      <c r="Y203" s="16" t="n"/>
-      <c r="Z203" s="16" t="n"/>
-      <c r="AA203" s="16" t="n"/>
-      <c r="AB203" s="16" t="n"/>
-      <c r="AC203" s="16" t="n"/>
-      <c r="AD203" s="16" t="n"/>
-      <c r="AE203" s="16" t="n"/>
-      <c r="AF203" s="16" t="n"/>
-      <c r="AG203" s="16" t="n"/>
-      <c r="AH203" s="16" t="n"/>
-      <c r="AI203" s="17">
-        <f>IFERROR(AF203+AG203+AH203,"")</f>
-        <v/>
-      </c>
-      <c r="AJ203" s="16" t="n"/>
-      <c r="AK203" s="16" t="n"/>
-    </row>
+    <row r="203" ht="18" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A2:AK2"/>
   <mergeCells count="7">
